--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18438" uniqueCount="1451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18409" uniqueCount="1450">
   <si>
     <t>Property</t>
   </si>
@@ -60,10 +60,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T07:40:29+00:00</t>
+    <t>2026-08-24T13:49:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -117,13 +120,10 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -344,7 +344,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/mii-vs-labor-interpretation-eigenschaften-snomedct|2027.0.0</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/mii-vs-labor-interpretation-eigenschaften-snomedct</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -483,7 +483,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/QuelleKlinischesBezugsdatum|2027.0.0</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/QuelleKlinischesBezugsdatum</t>
   </si>
   <si>
     <t>mii-lm-labor</t>
@@ -504,7 +504,7 @@
     <t>logical</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Element|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Element</t>
   </si>
   <si>
     <t>specialization</t>
@@ -962,7 +962,7 @@
     <t>ServiceRequest</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/ServiceRequest|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/ServiceRequest</t>
   </si>
   <si>
     <t>diagnostic request
@@ -1805,7 +1805,7 @@
     <t>Many laboratory and radiology procedure codes embed the specimen/organ system in the test order name, for example,  serum or serum/plasma glucose, or a chest x-ray. The specimen might not be recorded separately from the test code.</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/ValueSetOrderCodes|2027.0.0</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/ValueSetOrderCodes</t>
   </si>
   <si>
     <t>ServiceRequest.code.id</t>
@@ -2134,7 +2134,7 @@
     <t>A location type where services are delivered.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType|3.0.0</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ServiceDeliveryLocationRoleType</t>
   </si>
   <si>
     <t>ServiceRequest.locationReference</t>
@@ -2328,7 +2328,7 @@
     <t>DiagnosticReport</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/DiagnosticReport|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/DiagnosticReport</t>
   </si>
   <si>
     <t>Report
@@ -2860,7 +2860,7 @@
     <t>QuelleKlinischesBezugsdatum</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-labor/StructureDefinition/QuelleKlinischesBezugsdatum|2027.0.0}
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-labor/StructureDefinition/QuelleKlinischesBezugsdatum}
 </t>
   </si>
   <si>
@@ -3163,7 +3163,7 @@
     <t>Observation</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Observation|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Observation</t>
   </si>
   <si>
     <t>Vital Signs
@@ -3180,7 +3180,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}mii-lab-2:Falls kein Laborwert verfügbar ist, muss eine dataAbsentReason angegeben werden {hasMember.exists() xor value.exists().not() implies dataAbsentReason.exists()}mii-lab-3:Every coding of a coded laboratory result contains both system and code. {value.ofType(CodeableConcept).coding.all(system.exists() and code.exists())}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}mii-lab-2:Falls kein Laborwert verfügbar ist, muss eine dataAbsentReason angegeben werden {hasMember.exists() or value.exists() or dataAbsentReason.exists()}</t>
   </si>
   <si>
     <t>Observation.id</t>
@@ -3237,7 +3237,7 @@
     <t>interpretationsbeeinflussendeEigenschaft</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-labor/StructureDefinition/InterpretationsbeeinflussendeEigenschaft|2027.0.0}
+    <t xml:space="preserve">Extension {https://www.medizininformatik-initiative.de/fhir/core/modul-labor/StructureDefinition/InterpretationsbeeinflussendeEigenschaft}
 </t>
   </si>
   <si>
@@ -3300,7 +3300,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/mii-vs-labor-identifier-type-codes|2027.0.0</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/mii-vs-labor-identifier-type-codes</t>
   </si>
   <si>
     <t>Observation.identifier:analyseBefundCode.type.id</t>
@@ -3409,6 +3409,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(ServiceRequest)
+</t>
+  </si>
+  <si>
     <t>Basiert auf</t>
   </si>
   <si>
@@ -3577,40 +3581,78 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
+  </si>
+  <si>
+    <t>Observation.code.id</t>
+  </si>
+  <si>
+    <t>Observation.code.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc</t>
+  </si>
+  <si>
+    <t>loinc</t>
+  </si>
+  <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://loinc.org"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>Intensional Value Set Definition: LOINC {  {    STATUS in {ACTIVE}    CLASSTYPE in {1}    CLASS exclude {CHALSKIN, H&amp;P.HX.LAB, H&amp;P.HX, NR STATS, PATH.PROTOCOLS.*}  } }</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/uv/ips/ValueSet/results-laboratory-pathology-observations-uv-ips|2.0.1</t>
-  </si>
-  <si>
-    <t>Observation.code.id</t>
-  </si>
-  <si>
-    <t>Observation.code.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.code.coding.userSelected</t>
+    <t>http://hl7.org/fhir/uv/ips/ValueSet/results-laboratory-pathology-observations-uv-ips</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.id</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.extension</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.system</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.version</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.code</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.display</t>
+  </si>
+  <si>
+    <t>Observation.code.coding:loinc.userSelected</t>
   </si>
   <si>
     <t>Observation.code.text</t>
@@ -3805,7 +3847,7 @@
     <t>pqTranslation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {extension-quantity-translation|5.3.0}
+    <t xml:space="preserve">Extension {extension-quantity-translation}
 </t>
   </si>
   <si>
@@ -3862,7 +3904,7 @@
     <t>quantityPrecision</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {quantity-precision|5.3.0}
+    <t xml:space="preserve">Extension {quantity-precision}
 </t>
   </si>
   <si>
@@ -3984,6 +4026,9 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Laborergebnis-codiert</t>
+  </si>
+  <si>
     <t>Observation.value[x]:valueCodeableConcept.id</t>
   </si>
   <si>
@@ -3996,85 +4041,46 @@
     <t>Observation.value[x].coding</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ</t>
-  </si>
-  <si>
-    <t>qualitativ</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Laborergebnis-qualitativ|2027.0.0</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.id</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.id</t>
   </si>
   <si>
     <t>Observation.value[x].coding.id</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.extension</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.extension</t>
   </si>
   <si>
     <t>Observation.value[x].coding.extension</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.system</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.system</t>
   </si>
   <si>
     <t>Observation.value[x].coding.system</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.version</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.version</t>
   </si>
   <si>
     <t>Observation.value[x].coding.version</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.code</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.code</t>
   </si>
   <si>
     <t>Observation.value[x].coding.code</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.display</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.display</t>
   </si>
   <si>
     <t>Observation.value[x].coding.display</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:qualitativ.userSelected</t>
+    <t>Observation.value[x]:valueCodeableConcept.coding.userSelected</t>
   </si>
   <si>
     <t>Observation.value[x].coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ</t>
-  </si>
-  <si>
-    <t>semiquantitativ</t>
-  </si>
-  <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Laborergebnis-semiquantitativ|2027.0.0</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.system</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.version</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.code</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.display</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding:semiquantitativ.userSelected</t>
   </si>
   <si>
     <t>Observation.value[x]:valueCodeableConcept.text</t>
@@ -4477,12 +4483,6 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Observation.component.value[x]</t>
@@ -4727,98 +4727,100 @@
       <c r="A8" t="s" s="2">
         <v>14</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" t="s" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -4897,43 +4899,45 @@
       <c r="A30" t="s" s="2">
         <v>14</v>
       </c>
-      <c r="B30" s="2"/>
+      <c r="B30" t="s" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>148</v>
@@ -4941,54 +4945,54 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43">
@@ -5075,43 +5079,45 @@
       <c r="A53" t="s" s="2">
         <v>14</v>
       </c>
-      <c r="B53" s="2"/>
+      <c r="B53" t="s" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>157</v>
@@ -5119,27 +5125,27 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>158</v>
@@ -5147,7 +5153,7 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>154</v>
@@ -5155,7 +5161,7 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>159</v>
@@ -5163,10 +5169,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66">
@@ -5237,43 +5243,45 @@
       <c r="A74" t="s" s="2">
         <v>14</v>
       </c>
-      <c r="B74" s="2"/>
+      <c r="B74" t="s" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>306</v>
@@ -5281,7 +5289,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>306</v>
@@ -5289,21 +5297,21 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B83" t="s" s="2">
         <v>307</v>
@@ -5311,7 +5319,7 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B84" t="s" s="2">
         <v>308</v>
@@ -5319,7 +5327,7 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B85" t="s" s="2">
         <v>309</v>
@@ -5327,10 +5335,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87">
@@ -5402,44 +5410,44 @@
         <v>14</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B100" t="s" s="2">
         <v>741</v>
@@ -5447,7 +5455,7 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B101" t="s" s="2">
         <v>741</v>
@@ -5455,21 +5463,21 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B102" s="2"/>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B104" t="s" s="2">
         <v>307</v>
@@ -5477,7 +5485,7 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B105" t="s" s="2">
         <v>742</v>
@@ -5485,7 +5493,7 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B106" t="s" s="2">
         <v>743</v>
@@ -5493,10 +5501,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108">
@@ -5567,43 +5575,45 @@
       <c r="A116" t="s" s="2">
         <v>14</v>
       </c>
-      <c r="B116" s="2"/>
+      <c r="B116" t="s" s="2">
+        <v>15</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B121" t="s" s="2">
         <v>1005</v>
@@ -5611,7 +5621,7 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B122" t="s" s="2">
         <v>1006</v>
@@ -5619,21 +5629,21 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B123" s="2"/>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>307</v>
@@ -5641,7 +5651,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B126" t="s" s="2">
         <v>1007</v>
@@ -5649,7 +5659,7 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B127" t="s" s="2">
         <v>1008</v>
@@ -5657,10 +5667,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129">
@@ -5678,7 +5688,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK551"/>
+  <dimension ref="A1:AK550"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.24609375" customWidth="true" bestFit="true"/>
@@ -5707,7 +5717,7 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="140.3671875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="108.5078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="100.98046875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -5836,10 +5846,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" t="s" s="2">
@@ -5865,7 +5875,7 @@
         <v>81</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N2" t="s" s="2">
         <v>82</v>
@@ -5919,7 +5929,7 @@
         <v>77</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AH2" t="s" s="2">
         <v>78</v>
@@ -6071,7 +6081,7 @@
         <v>92</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N4" t="s" s="2">
         <v>82</v>
@@ -7088,10 +7098,10 @@
         <v>144</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" t="s" s="2">
@@ -7117,7 +7127,7 @@
         <v>81</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N14" t="s" s="2">
         <v>82</v>
@@ -7171,7 +7181,7 @@
         <v>77</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>78</v>
@@ -7323,7 +7333,7 @@
         <v>92</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N16" t="s" s="2">
         <v>82</v>
@@ -25372,7 +25382,7 @@
         <v>86</v>
       </c>
       <c r="I189" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J189" t="s" s="2">
         <v>77</v>
@@ -39456,7 +39466,7 @@
         <v>92</v>
       </c>
       <c r="M323" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N323" t="s" s="2">
         <v>82</v>
@@ -44910,7 +44920,7 @@
         <v>92</v>
       </c>
       <c r="M375" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N375" t="s" s="2">
         <v>82</v>
@@ -47429,17 +47439,17 @@
         <v>80</v>
       </c>
       <c r="L399" t="s" s="2">
-        <v>512</v>
+        <v>1087</v>
       </c>
       <c r="M399" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="N399" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O399" s="2"/>
       <c r="P399" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="Q399" t="s" s="2">
         <v>77</v>
@@ -47508,14 +47518,14 @@
         <v>1001</v>
       </c>
       <c r="B400" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="C400" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="D400" s="2"/>
       <c r="E400" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F400" s="2"/>
       <c r="G400" t="s" s="2">
@@ -47534,16 +47544,16 @@
         <v>80</v>
       </c>
       <c r="L400" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="M400" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="N400" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="O400" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="P400" s="2"/>
       <c r="Q400" t="s" s="2">
@@ -47593,7 +47603,7 @@
         <v>77</v>
       </c>
       <c r="AG400" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="AH400" t="s" s="2">
         <v>78</v>
@@ -47613,10 +47623,10 @@
         <v>1001</v>
       </c>
       <c r="B401" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C401" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D401" s="2"/>
       <c r="E401" t="s" s="2">
@@ -47645,13 +47655,13 @@
         <v>12</v>
       </c>
       <c r="N401" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="O401" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="P401" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="Q401" t="s" s="2">
         <v>77</v>
@@ -47679,10 +47689,10 @@
         <v>151</v>
       </c>
       <c r="Z401" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="AA401" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="AB401" t="s" s="2">
         <v>77</v>
@@ -47700,7 +47710,7 @@
         <v>77</v>
       </c>
       <c r="AG401" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="AH401" t="s" s="2">
         <v>86</v>
@@ -47720,10 +47730,10 @@
         <v>1001</v>
       </c>
       <c r="B402" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C402" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D402" s="2"/>
       <c r="E402" t="s" s="2">
@@ -47752,13 +47762,13 @@
         <v>535</v>
       </c>
       <c r="N402" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="O402" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="P402" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="Q402" t="s" s="2">
         <v>77</v>
@@ -47786,10 +47796,10 @@
         <v>373</v>
       </c>
       <c r="Z402" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AA402" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="AB402" t="s" s="2">
         <v>77</v>
@@ -47807,7 +47817,7 @@
         <v>77</v>
       </c>
       <c r="AG402" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="AH402" t="s" s="2">
         <v>78</v>
@@ -47827,10 +47837,10 @@
         <v>1001</v>
       </c>
       <c r="B403" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C403" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D403" s="2"/>
       <c r="E403" t="s" s="2">
@@ -47930,10 +47940,10 @@
         <v>1001</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D404" s="2"/>
       <c r="E404" t="s" s="2">
@@ -48035,10 +48045,10 @@
         <v>1001</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D405" s="2"/>
       <c r="E405" t="s" s="2">
@@ -48140,10 +48150,10 @@
         <v>1001</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D406" s="2"/>
       <c r="E406" t="s" s="2">
@@ -48243,10 +48253,10 @@
         <v>1001</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D407" s="2"/>
       <c r="E407" t="s" s="2">
@@ -48348,10 +48358,10 @@
         <v>1001</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D408" s="2"/>
       <c r="E408" t="s" s="2">
@@ -48455,10 +48465,10 @@
         <v>1001</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D409" s="2"/>
       <c r="E409" t="s" s="2">
@@ -48560,10 +48570,10 @@
         <v>1001</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D410" s="2"/>
       <c r="E410" t="s" s="2">
@@ -48665,10 +48675,10 @@
         <v>1001</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D411" s="2"/>
       <c r="E411" t="s" s="2">
@@ -48770,10 +48780,10 @@
         <v>1001</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D412" s="2"/>
       <c r="E412" t="s" s="2">
@@ -48877,13 +48887,13 @@
         <v>1001</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D413" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="E413" t="s" s="2">
         <v>77</v>
@@ -48986,10 +48996,10 @@
         <v>1001</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D414" s="2"/>
       <c r="E414" t="s" s="2">
@@ -49089,10 +49099,10 @@
         <v>1001</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D415" s="2"/>
       <c r="E415" t="s" s="2">
@@ -49194,10 +49204,10 @@
         <v>1001</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D416" s="2"/>
       <c r="E416" t="s" s="2">
@@ -49301,10 +49311,10 @@
         <v>1001</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D417" s="2"/>
       <c r="E417" t="s" s="2">
@@ -49406,10 +49416,10 @@
         <v>1001</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D418" s="2"/>
       <c r="E418" t="s" s="2">
@@ -49511,10 +49521,10 @@
         <v>1001</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D419" s="2"/>
       <c r="E419" t="s" s="2">
@@ -49616,10 +49626,10 @@
         <v>1001</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D420" s="2"/>
       <c r="E420" t="s" s="2">
@@ -49723,13 +49733,13 @@
         <v>1001</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D421" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="E421" t="s" s="2">
         <v>77</v>
@@ -49832,10 +49842,10 @@
         <v>1001</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D422" s="2"/>
       <c r="E422" t="s" s="2">
@@ -49935,10 +49945,10 @@
         <v>1001</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D423" s="2"/>
       <c r="E423" t="s" s="2">
@@ -50040,10 +50050,10 @@
         <v>1001</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D424" s="2"/>
       <c r="E424" t="s" s="2">
@@ -50147,10 +50157,10 @@
         <v>1001</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D425" s="2"/>
       <c r="E425" t="s" s="2">
@@ -50252,10 +50262,10 @@
         <v>1001</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D426" s="2"/>
       <c r="E426" t="s" s="2">
@@ -50357,10 +50367,10 @@
         <v>1001</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D427" s="2"/>
       <c r="E427" t="s" s="2">
@@ -50462,10 +50472,10 @@
         <v>1001</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D428" s="2"/>
       <c r="E428" t="s" s="2">
@@ -50569,10 +50579,10 @@
         <v>1001</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="D429" s="2"/>
       <c r="E429" t="s" s="2">
@@ -50676,14 +50686,14 @@
         <v>1001</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D430" s="2"/>
       <c r="E430" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="F430" s="2"/>
       <c r="G430" t="s" s="2">
@@ -50708,13 +50718,13 @@
         <v>67</v>
       </c>
       <c r="N430" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="O430" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="P430" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="Q430" t="s" s="2">
         <v>77</v>
@@ -50739,13 +50749,13 @@
         <v>77</v>
       </c>
       <c r="Y430" t="s" s="2">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="Z430" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="AA430" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="AB430" t="s" s="2">
         <v>77</v>
@@ -50763,7 +50773,7 @@
         <v>77</v>
       </c>
       <c r="AG430" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="AH430" t="s" s="2">
         <v>86</v>
@@ -50783,10 +50793,10 @@
         <v>1001</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="D431" s="2"/>
       <c r="E431" t="s" s="2">
@@ -50886,10 +50896,10 @@
         <v>1001</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D432" s="2"/>
       <c r="E432" t="s" s="2">
@@ -50991,10 +51001,10 @@
         <v>1001</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D433" s="2"/>
       <c r="E433" t="s" s="2">
@@ -51066,16 +51076,14 @@
         <v>77</v>
       </c>
       <c r="AC433" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD433" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="AD433" s="2"/>
       <c r="AE433" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF433" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG433" t="s" s="2">
         <v>442</v>
@@ -51098,10 +51106,10 @@
         <v>1001</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D434" s="2"/>
       <c r="E434" t="s" s="2">
@@ -51201,10 +51209,10 @@
         <v>1001</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D435" s="2"/>
       <c r="E435" t="s" s="2">
@@ -51306,10 +51314,10 @@
         <v>1001</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D436" s="2"/>
       <c r="E436" t="s" s="2">
@@ -51413,10 +51421,10 @@
         <v>1001</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="D437" s="2"/>
       <c r="E437" t="s" s="2">
@@ -51430,7 +51438,7 @@
         <v>86</v>
       </c>
       <c r="I437" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J437" t="s" s="2">
         <v>77</v>
@@ -51518,10 +51526,10 @@
         <v>1001</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D438" s="2"/>
       <c r="E438" t="s" s="2">
@@ -51623,10 +51631,10 @@
         <v>1001</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C439" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D439" s="2"/>
       <c r="E439" t="s" s="2">
@@ -51728,10 +51736,10 @@
         <v>1001</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D440" s="2"/>
       <c r="E440" t="s" s="2">
@@ -51835,12 +51843,14 @@
         <v>1001</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C441" t="s" s="2">
-        <v>1154</v>
-      </c>
-      <c r="D441" s="2"/>
+        <v>1147</v>
+      </c>
+      <c r="D441" t="s" s="2">
+        <v>1156</v>
+      </c>
       <c r="E441" t="s" s="2">
         <v>77</v>
       </c>
@@ -51849,10 +51859,10 @@
         <v>78</v>
       </c>
       <c r="H441" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I441" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J441" t="s" s="2">
         <v>77</v>
@@ -51861,19 +51871,19 @@
         <v>80</v>
       </c>
       <c r="L441" t="s" s="2">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="M441" t="s" s="2">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="N441" t="s" s="2">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="O441" t="s" s="2">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="P441" t="s" s="2">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="Q441" t="s" s="2">
         <v>77</v>
@@ -51883,7 +51893,7 @@
         <v>77</v>
       </c>
       <c r="T441" t="s" s="2">
-        <v>77</v>
+        <v>1157</v>
       </c>
       <c r="U441" t="s" s="2">
         <v>77</v>
@@ -51898,13 +51908,13 @@
         <v>77</v>
       </c>
       <c r="Y441" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="Z441" t="s" s="2">
-        <v>77</v>
+        <v>1158</v>
       </c>
       <c r="AA441" t="s" s="2">
-        <v>77</v>
+        <v>1159</v>
       </c>
       <c r="AB441" t="s" s="2">
         <v>77</v>
@@ -51922,13 +51932,13 @@
         <v>77</v>
       </c>
       <c r="AG441" t="s" s="2">
-        <v>467</v>
+        <v>442</v>
       </c>
       <c r="AH441" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI441" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ441" t="s" s="2">
         <v>77</v>
@@ -51942,10 +51952,10 @@
         <v>1001</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>1155</v>
+        <v>1160</v>
       </c>
       <c r="C442" t="s" s="2">
-        <v>1155</v>
+        <v>1148</v>
       </c>
       <c r="D442" s="2"/>
       <c r="E442" t="s" s="2">
@@ -51953,35 +51963,31 @@
       </c>
       <c r="F442" s="2"/>
       <c r="G442" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H442" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I442" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J442" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K442" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L442" t="s" s="2">
-        <v>879</v>
+        <v>87</v>
       </c>
       <c r="M442" t="s" s="2">
-        <v>606</v>
+        <v>88</v>
       </c>
       <c r="N442" t="s" s="2">
-        <v>1156</v>
-      </c>
-      <c r="O442" t="s" s="2">
-        <v>1157</v>
-      </c>
-      <c r="P442" t="s" s="2">
-        <v>1158</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O442" s="2"/>
+      <c r="P442" s="2"/>
       <c r="Q442" t="s" s="2">
         <v>77</v>
       </c>
@@ -52029,7 +52035,7 @@
         <v>77</v>
       </c>
       <c r="AG442" t="s" s="2">
-        <v>1155</v>
+        <v>90</v>
       </c>
       <c r="AH442" t="s" s="2">
         <v>78</v>
@@ -52041,7 +52047,7 @@
         <v>77</v>
       </c>
       <c r="AK442" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="443">
@@ -52049,21 +52055,21 @@
         <v>1001</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>1159</v>
+        <v>1149</v>
       </c>
       <c r="D443" s="2"/>
       <c r="E443" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F443" s="2"/>
       <c r="G443" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H443" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I443" t="s" s="2">
         <v>77</v>
@@ -52075,15 +52081,17 @@
         <v>77</v>
       </c>
       <c r="L443" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M443" t="s" s="2">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="N443" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O443" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O443" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P443" s="2"/>
       <c r="Q443" t="s" s="2">
         <v>77</v>
@@ -52120,31 +52128,31 @@
         <v>77</v>
       </c>
       <c r="AC443" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD443" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE443" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF443" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG443" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AH443" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI443" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ443" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK443" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="444">
@@ -52152,44 +52160,46 @@
         <v>1001</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="C444" t="s" s="2">
-        <v>1160</v>
+        <v>1150</v>
       </c>
       <c r="D444" s="2"/>
       <c r="E444" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F444" s="2"/>
       <c r="G444" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H444" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I444" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J444" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K444" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L444" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="M444" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="N444" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="O444" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="P444" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="P444" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="Q444" t="s" s="2">
         <v>77</v>
       </c>
@@ -52225,31 +52235,31 @@
         <v>77</v>
       </c>
       <c r="AC444" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD444" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE444" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF444" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG444" t="s" s="2">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="AH444" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI444" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ444" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK444" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="445">
@@ -52257,10 +52267,10 @@
         <v>1001</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>1161</v>
+        <v>1151</v>
       </c>
       <c r="D445" s="2"/>
       <c r="E445" t="s" s="2">
@@ -52286,13 +52296,13 @@
         <v>87</v>
       </c>
       <c r="M445" t="s" s="2">
-        <v>611</v>
+        <v>122</v>
       </c>
       <c r="N445" t="s" s="2">
-        <v>612</v>
+        <v>123</v>
       </c>
       <c r="O445" t="s" s="2">
-        <v>613</v>
+        <v>124</v>
       </c>
       <c r="P445" s="2"/>
       <c r="Q445" t="s" s="2">
@@ -52342,7 +52352,7 @@
         <v>77</v>
       </c>
       <c r="AG445" t="s" s="2">
-        <v>614</v>
+        <v>125</v>
       </c>
       <c r="AH445" t="s" s="2">
         <v>78</v>
@@ -52351,7 +52361,7 @@
         <v>86</v>
       </c>
       <c r="AJ445" t="s" s="2">
-        <v>615</v>
+        <v>77</v>
       </c>
       <c r="AK445" t="s" s="2">
         <v>108</v>
@@ -52362,10 +52372,10 @@
         <v>1001</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>1162</v>
+        <v>1152</v>
       </c>
       <c r="D446" s="2"/>
       <c r="E446" t="s" s="2">
@@ -52373,13 +52383,13 @@
       </c>
       <c r="F446" s="2"/>
       <c r="G446" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H446" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I446" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J446" t="s" s="2">
         <v>77</v>
@@ -52388,18 +52398,18 @@
         <v>80</v>
       </c>
       <c r="L446" t="s" s="2">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="M446" t="s" s="2">
-        <v>617</v>
+        <v>128</v>
       </c>
       <c r="N446" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="O446" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="P446" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="O446" s="2"/>
+      <c r="P446" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="Q446" t="s" s="2">
         <v>77</v>
       </c>
@@ -52423,13 +52433,13 @@
         <v>77</v>
       </c>
       <c r="Y446" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="Z446" t="s" s="2">
-        <v>620</v>
+        <v>77</v>
       </c>
       <c r="AA446" t="s" s="2">
-        <v>621</v>
+        <v>77</v>
       </c>
       <c r="AB446" t="s" s="2">
         <v>77</v>
@@ -52447,7 +52457,7 @@
         <v>77</v>
       </c>
       <c r="AG446" t="s" s="2">
-        <v>622</v>
+        <v>131</v>
       </c>
       <c r="AH446" t="s" s="2">
         <v>78</v>
@@ -52467,10 +52477,10 @@
         <v>1001</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>1163</v>
+        <v>1153</v>
       </c>
       <c r="D447" s="2"/>
       <c r="E447" t="s" s="2">
@@ -52493,18 +52503,18 @@
         <v>80</v>
       </c>
       <c r="L447" t="s" s="2">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="M447" t="s" s="2">
-        <v>624</v>
+        <v>133</v>
       </c>
       <c r="N447" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="O447" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="P447" s="2"/>
+        <v>134</v>
+      </c>
+      <c r="O447" s="2"/>
+      <c r="P447" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="Q447" t="s" s="2">
         <v>77</v>
       </c>
@@ -52552,7 +52562,7 @@
         <v>77</v>
       </c>
       <c r="AG447" t="s" s="2">
-        <v>627</v>
+        <v>136</v>
       </c>
       <c r="AH447" t="s" s="2">
         <v>78</v>
@@ -52572,10 +52582,10 @@
         <v>1001</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>1164</v>
+        <v>1154</v>
       </c>
       <c r="D448" s="2"/>
       <c r="E448" t="s" s="2">
@@ -52598,18 +52608,20 @@
         <v>80</v>
       </c>
       <c r="L448" t="s" s="2">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="M448" t="s" s="2">
-        <v>629</v>
+        <v>139</v>
       </c>
       <c r="N448" t="s" s="2">
-        <v>630</v>
+        <v>140</v>
       </c>
       <c r="O448" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="P448" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="P448" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="Q448" t="s" s="2">
         <v>77</v>
       </c>
@@ -52657,7 +52669,7 @@
         <v>77</v>
       </c>
       <c r="AG448" t="s" s="2">
-        <v>632</v>
+        <v>143</v>
       </c>
       <c r="AH448" t="s" s="2">
         <v>78</v>
@@ -52677,10 +52689,10 @@
         <v>1001</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D449" s="2"/>
       <c r="E449" t="s" s="2">
@@ -52691,7 +52703,7 @@
         <v>78</v>
       </c>
       <c r="H449" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I449" t="s" s="2">
         <v>77</v>
@@ -52703,18 +52715,20 @@
         <v>80</v>
       </c>
       <c r="L449" t="s" s="2">
-        <v>703</v>
+        <v>87</v>
       </c>
       <c r="M449" t="s" s="2">
-        <v>1166</v>
+        <v>463</v>
       </c>
       <c r="N449" t="s" s="2">
-        <v>1167</v>
+        <v>464</v>
       </c>
       <c r="O449" t="s" s="2">
-        <v>1168</v>
-      </c>
-      <c r="P449" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="P449" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="Q449" t="s" s="2">
         <v>77</v>
       </c>
@@ -52762,13 +52776,13 @@
         <v>77</v>
       </c>
       <c r="AG449" t="s" s="2">
-        <v>1165</v>
+        <v>467</v>
       </c>
       <c r="AH449" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI449" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ449" t="s" s="2">
         <v>77</v>
@@ -52782,18 +52796,18 @@
         <v>1001</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="D450" s="2"/>
       <c r="E450" t="s" s="2">
-        <v>889</v>
+        <v>77</v>
       </c>
       <c r="F450" s="2"/>
       <c r="G450" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H450" t="s" s="2">
         <v>86</v>
@@ -52808,19 +52822,19 @@
         <v>80</v>
       </c>
       <c r="L450" t="s" s="2">
-        <v>635</v>
+        <v>879</v>
       </c>
       <c r="M450" t="s" s="2">
-        <v>636</v>
+        <v>606</v>
       </c>
       <c r="N450" t="s" s="2">
+        <v>1169</v>
+      </c>
+      <c r="O450" t="s" s="2">
         <v>1170</v>
       </c>
-      <c r="O450" t="s" s="2">
+      <c r="P450" t="s" s="2">
         <v>1171</v>
-      </c>
-      <c r="P450" t="s" s="2">
-        <v>1172</v>
       </c>
       <c r="Q450" t="s" s="2">
         <v>77</v>
@@ -52869,7 +52883,7 @@
         <v>77</v>
       </c>
       <c r="AG450" t="s" s="2">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="AH450" t="s" s="2">
         <v>78</v>
@@ -52889,10 +52903,10 @@
         <v>1001</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D451" s="2"/>
       <c r="E451" t="s" s="2">
@@ -52992,10 +53006,10 @@
         <v>1001</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="C452" t="s" s="2">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="D452" s="2"/>
       <c r="E452" t="s" s="2">
@@ -53097,10 +53111,10 @@
         <v>1001</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="D453" s="2"/>
       <c r="E453" t="s" s="2">
@@ -53202,10 +53216,10 @@
         <v>1001</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="D454" s="2"/>
       <c r="E454" t="s" s="2">
@@ -53307,10 +53321,10 @@
         <v>1001</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="D455" s="2"/>
       <c r="E455" t="s" s="2">
@@ -53412,10 +53426,10 @@
         <v>1001</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="D456" s="2"/>
       <c r="E456" t="s" s="2">
@@ -53517,24 +53531,24 @@
         <v>1001</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="D457" s="2"/>
       <c r="E457" t="s" s="2">
-        <v>1180</v>
+        <v>77</v>
       </c>
       <c r="F457" s="2"/>
       <c r="G457" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H457" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I457" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J457" t="s" s="2">
         <v>77</v>
@@ -53543,20 +53557,18 @@
         <v>80</v>
       </c>
       <c r="L457" t="s" s="2">
-        <v>173</v>
+        <v>703</v>
       </c>
       <c r="M457" t="s" s="2">
+        <v>1179</v>
+      </c>
+      <c r="N457" t="s" s="2">
+        <v>1180</v>
+      </c>
+      <c r="O457" t="s" s="2">
         <v>1181</v>
       </c>
-      <c r="N457" t="s" s="2">
-        <v>1182</v>
-      </c>
-      <c r="O457" t="s" s="2">
-        <v>1183</v>
-      </c>
-      <c r="P457" t="s" s="2">
-        <v>1184</v>
-      </c>
+      <c r="P457" s="2"/>
       <c r="Q457" t="s" s="2">
         <v>77</v>
       </c>
@@ -53604,19 +53616,19 @@
         <v>77</v>
       </c>
       <c r="AG457" t="s" s="2">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="AH457" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI457" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ457" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK457" t="s" s="2">
-        <v>1185</v>
+        <v>108</v>
       </c>
     </row>
     <row r="458">
@@ -53624,14 +53636,14 @@
         <v>1001</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="D458" s="2"/>
       <c r="E458" t="s" s="2">
-        <v>77</v>
+        <v>889</v>
       </c>
       <c r="F458" s="2"/>
       <c r="G458" t="s" s="2">
@@ -53641,25 +53653,29 @@
         <v>86</v>
       </c>
       <c r="I458" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J458" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K458" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L458" t="s" s="2">
-        <v>87</v>
+        <v>635</v>
       </c>
       <c r="M458" t="s" s="2">
-        <v>906</v>
+        <v>636</v>
       </c>
       <c r="N458" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="O458" s="2"/>
-      <c r="P458" s="2"/>
+        <v>1183</v>
+      </c>
+      <c r="O458" t="s" s="2">
+        <v>1184</v>
+      </c>
+      <c r="P458" t="s" s="2">
+        <v>1185</v>
+      </c>
       <c r="Q458" t="s" s="2">
         <v>77</v>
       </c>
@@ -53707,7 +53723,7 @@
         <v>77</v>
       </c>
       <c r="AG458" t="s" s="2">
-        <v>90</v>
+        <v>1182</v>
       </c>
       <c r="AH458" t="s" s="2">
         <v>78</v>
@@ -53719,7 +53735,7 @@
         <v>77</v>
       </c>
       <c r="AK458" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="459">
@@ -53727,10 +53743,10 @@
         <v>1001</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="C459" t="s" s="2">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="D459" s="2"/>
       <c r="E459" t="s" s="2">
@@ -53741,7 +53757,7 @@
         <v>78</v>
       </c>
       <c r="H459" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I459" t="s" s="2">
         <v>77</v>
@@ -53753,13 +53769,13 @@
         <v>77</v>
       </c>
       <c r="L459" t="s" s="2">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M459" t="s" s="2">
-        <v>32</v>
+        <v>88</v>
       </c>
       <c r="N459" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="O459" s="2"/>
       <c r="P459" s="2"/>
@@ -53798,29 +53814,31 @@
         <v>77</v>
       </c>
       <c r="AC459" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AD459" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AD459" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AE459" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF459" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG459" t="s" s="2">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="AH459" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI459" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ459" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK459" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="460">
@@ -53828,26 +53846,24 @@
         <v>1001</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="C460" t="s" s="2">
         <v>1187</v>
       </c>
-      <c r="D460" t="s" s="2">
-        <v>910</v>
-      </c>
+      <c r="D460" s="2"/>
       <c r="E460" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F460" s="2"/>
       <c r="G460" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H460" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I460" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J460" t="s" s="2">
         <v>77</v>
@@ -53856,15 +53872,17 @@
         <v>77</v>
       </c>
       <c r="L460" t="s" s="2">
-        <v>911</v>
+        <v>92</v>
       </c>
       <c r="M460" t="s" s="2">
-        <v>1189</v>
+        <v>112</v>
       </c>
       <c r="N460" t="s" s="2">
-        <v>912</v>
-      </c>
-      <c r="O460" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O460" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P460" s="2"/>
       <c r="Q460" t="s" s="2">
         <v>77</v>
@@ -53901,16 +53919,16 @@
         <v>77</v>
       </c>
       <c r="AC460" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD460" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE460" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF460" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG460" t="s" s="2">
         <v>96</v>
@@ -53922,7 +53940,7 @@
         <v>79</v>
       </c>
       <c r="AJ460" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK460" t="s" s="2">
         <v>84</v>
@@ -53933,10 +53951,10 @@
         <v>1001</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="C461" t="s" s="2">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="D461" s="2"/>
       <c r="E461" t="s" s="2">
@@ -53950,24 +53968,26 @@
         <v>86</v>
       </c>
       <c r="I461" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J461" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K461" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L461" t="s" s="2">
-        <v>173</v>
+        <v>87</v>
       </c>
       <c r="M461" t="s" s="2">
-        <v>914</v>
+        <v>611</v>
       </c>
       <c r="N461" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="O461" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="O461" t="s" s="2">
+        <v>613</v>
+      </c>
       <c r="P461" s="2"/>
       <c r="Q461" t="s" s="2">
         <v>77</v>
@@ -54016,7 +54036,7 @@
         <v>77</v>
       </c>
       <c r="AG461" t="s" s="2">
-        <v>916</v>
+        <v>614</v>
       </c>
       <c r="AH461" t="s" s="2">
         <v>78</v>
@@ -54025,10 +54045,10 @@
         <v>86</v>
       </c>
       <c r="AJ461" t="s" s="2">
-        <v>77</v>
+        <v>615</v>
       </c>
       <c r="AK461" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="462">
@@ -54036,10 +54056,10 @@
         <v>1001</v>
       </c>
       <c r="B462" t="s" s="2">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="C462" t="s" s="2">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="D462" s="2"/>
       <c r="E462" t="s" s="2">
@@ -54053,7 +54073,7 @@
         <v>86</v>
       </c>
       <c r="I462" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J462" t="s" s="2">
         <v>77</v>
@@ -54062,16 +54082,16 @@
         <v>80</v>
       </c>
       <c r="L462" t="s" s="2">
-        <v>333</v>
+        <v>98</v>
       </c>
       <c r="M462" t="s" s="2">
-        <v>919</v>
+        <v>617</v>
       </c>
       <c r="N462" t="s" s="2">
-        <v>239</v>
+        <v>618</v>
       </c>
       <c r="O462" t="s" s="2">
-        <v>1192</v>
+        <v>619</v>
       </c>
       <c r="P462" s="2"/>
       <c r="Q462" t="s" s="2">
@@ -54097,13 +54117,13 @@
         <v>77</v>
       </c>
       <c r="Y462" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="Z462" t="s" s="2">
-        <v>77</v>
+        <v>620</v>
       </c>
       <c r="AA462" t="s" s="2">
-        <v>77</v>
+        <v>621</v>
       </c>
       <c r="AB462" t="s" s="2">
         <v>77</v>
@@ -54121,7 +54141,7 @@
         <v>77</v>
       </c>
       <c r="AG462" t="s" s="2">
-        <v>1191</v>
+        <v>622</v>
       </c>
       <c r="AH462" t="s" s="2">
         <v>78</v>
@@ -54141,10 +54161,10 @@
         <v>1001</v>
       </c>
       <c r="B463" t="s" s="2">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="C463" t="s" s="2">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="D463" s="2"/>
       <c r="E463" t="s" s="2">
@@ -54155,10 +54175,10 @@
         <v>78</v>
       </c>
       <c r="H463" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I463" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J463" t="s" s="2">
         <v>77</v>
@@ -54167,18 +54187,18 @@
         <v>80</v>
       </c>
       <c r="L463" t="s" s="2">
-        <v>1194</v>
+        <v>167</v>
       </c>
       <c r="M463" t="s" s="2">
-        <v>1195</v>
+        <v>624</v>
       </c>
       <c r="N463" t="s" s="2">
-        <v>1196</v>
-      </c>
-      <c r="O463" s="2"/>
-      <c r="P463" t="s" s="2">
-        <v>1197</v>
-      </c>
+        <v>625</v>
+      </c>
+      <c r="O463" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="P463" s="2"/>
       <c r="Q463" t="s" s="2">
         <v>77</v>
       </c>
@@ -54226,13 +54246,13 @@
         <v>77</v>
       </c>
       <c r="AG463" t="s" s="2">
-        <v>1193</v>
+        <v>627</v>
       </c>
       <c r="AH463" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI463" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ463" t="s" s="2">
         <v>77</v>
@@ -54246,10 +54266,10 @@
         <v>1001</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>1198</v>
+        <v>1191</v>
       </c>
       <c r="C464" t="s" s="2">
-        <v>1198</v>
+        <v>1191</v>
       </c>
       <c r="D464" s="2"/>
       <c r="E464" t="s" s="2">
@@ -54263,7 +54283,7 @@
         <v>86</v>
       </c>
       <c r="I464" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J464" t="s" s="2">
         <v>77</v>
@@ -54272,20 +54292,18 @@
         <v>80</v>
       </c>
       <c r="L464" t="s" s="2">
-        <v>1199</v>
+        <v>87</v>
       </c>
       <c r="M464" t="s" s="2">
-        <v>1200</v>
+        <v>629</v>
       </c>
       <c r="N464" t="s" s="2">
-        <v>244</v>
+        <v>630</v>
       </c>
       <c r="O464" t="s" s="2">
-        <v>1201</v>
-      </c>
-      <c r="P464" t="s" s="2">
-        <v>1202</v>
-      </c>
+        <v>631</v>
+      </c>
+      <c r="P464" s="2"/>
       <c r="Q464" t="s" s="2">
         <v>77</v>
       </c>
@@ -54321,17 +54339,19 @@
         <v>77</v>
       </c>
       <c r="AC464" t="s" s="2">
-        <v>1203</v>
-      </c>
-      <c r="AD464" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AD464" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AE464" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF464" t="s" s="2">
-        <v>1204</v>
+        <v>77</v>
       </c>
       <c r="AG464" t="s" s="2">
-        <v>1198</v>
+        <v>632</v>
       </c>
       <c r="AH464" t="s" s="2">
         <v>78</v>
@@ -54340,7 +54360,7 @@
         <v>86</v>
       </c>
       <c r="AJ464" t="s" s="2">
-        <v>1205</v>
+        <v>77</v>
       </c>
       <c r="AK464" t="s" s="2">
         <v>108</v>
@@ -54351,20 +54371,18 @@
         <v>1001</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>1206</v>
+        <v>1192</v>
       </c>
       <c r="C465" t="s" s="2">
-        <v>1198</v>
-      </c>
-      <c r="D465" t="s" s="2">
-        <v>1207</v>
-      </c>
+        <v>1192</v>
+      </c>
+      <c r="D465" s="2"/>
       <c r="E465" t="s" s="2">
-        <v>77</v>
+        <v>1193</v>
       </c>
       <c r="F465" s="2"/>
       <c r="G465" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H465" t="s" s="2">
         <v>86</v>
@@ -54379,19 +54397,19 @@
         <v>80</v>
       </c>
       <c r="L465" t="s" s="2">
-        <v>243</v>
+        <v>173</v>
       </c>
       <c r="M465" t="s" s="2">
-        <v>1208</v>
+        <v>1194</v>
       </c>
       <c r="N465" t="s" s="2">
-        <v>1209</v>
+        <v>1195</v>
       </c>
       <c r="O465" t="s" s="2">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="P465" t="s" s="2">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="Q465" t="s" s="2">
         <v>77</v>
@@ -54440,19 +54458,19 @@
         <v>77</v>
       </c>
       <c r="AG465" t="s" s="2">
+        <v>1192</v>
+      </c>
+      <c r="AH465" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI465" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AJ465" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK465" t="s" s="2">
         <v>1198</v>
-      </c>
-      <c r="AH465" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI465" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="AJ465" t="s" s="2">
-        <v>1205</v>
-      </c>
-      <c r="AK465" t="s" s="2">
-        <v>108</v>
       </c>
     </row>
     <row r="466">
@@ -54460,10 +54478,10 @@
         <v>1001</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>1210</v>
+        <v>1199</v>
       </c>
       <c r="C466" t="s" s="2">
-        <v>1211</v>
+        <v>1199</v>
       </c>
       <c r="D466" s="2"/>
       <c r="E466" t="s" s="2">
@@ -54489,10 +54507,10 @@
         <v>87</v>
       </c>
       <c r="M466" t="s" s="2">
-        <v>88</v>
+        <v>906</v>
       </c>
       <c r="N466" t="s" s="2">
-        <v>89</v>
+        <v>907</v>
       </c>
       <c r="O466" s="2"/>
       <c r="P466" s="2"/>
@@ -54563,14 +54581,14 @@
         <v>1001</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>1212</v>
+        <v>1200</v>
       </c>
       <c r="C467" t="s" s="2">
-        <v>1213</v>
+        <v>1200</v>
       </c>
       <c r="D467" s="2"/>
       <c r="E467" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F467" s="2"/>
       <c r="G467" t="s" s="2">
@@ -54592,14 +54610,12 @@
         <v>92</v>
       </c>
       <c r="M467" t="s" s="2">
-        <v>112</v>
+        <v>33</v>
       </c>
       <c r="N467" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O467" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="O467" s="2"/>
       <c r="P467" s="2"/>
       <c r="Q467" t="s" s="2">
         <v>77</v>
@@ -54638,9 +54654,7 @@
       <c r="AC467" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="AD467" t="s" s="2">
-        <v>94</v>
-      </c>
+      <c r="AD467" s="2"/>
       <c r="AE467" t="s" s="2">
         <v>77</v>
       </c>
@@ -54668,13 +54682,13 @@
         <v>1001</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>1214</v>
+        <v>1201</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>1213</v>
+        <v>1200</v>
       </c>
       <c r="D468" t="s" s="2">
-        <v>1215</v>
+        <v>910</v>
       </c>
       <c r="E468" t="s" s="2">
         <v>77</v>
@@ -54684,10 +54698,10 @@
         <v>78</v>
       </c>
       <c r="H468" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I468" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J468" t="s" s="2">
         <v>77</v>
@@ -54696,17 +54710,15 @@
         <v>77</v>
       </c>
       <c r="L468" t="s" s="2">
-        <v>1216</v>
+        <v>911</v>
       </c>
       <c r="M468" t="s" s="2">
-        <v>1217</v>
+        <v>1202</v>
       </c>
       <c r="N468" t="s" s="2">
-        <v>1218</v>
-      </c>
-      <c r="O468" t="s" s="2">
-        <v>1219</v>
-      </c>
+        <v>912</v>
+      </c>
+      <c r="O468" s="2"/>
       <c r="P468" s="2"/>
       <c r="Q468" t="s" s="2">
         <v>77</v>
@@ -54764,7 +54776,7 @@
         <v>79</v>
       </c>
       <c r="AJ468" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AK468" t="s" s="2">
         <v>84</v>
@@ -54775,10 +54787,10 @@
         <v>1001</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1220</v>
+        <v>1203</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>1221</v>
+        <v>1203</v>
       </c>
       <c r="D469" s="2"/>
       <c r="E469" t="s" s="2">
@@ -54786,35 +54798,31 @@
       </c>
       <c r="F469" s="2"/>
       <c r="G469" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H469" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I469" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J469" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K469" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L469" t="s" s="2">
-        <v>1222</v>
+        <v>173</v>
       </c>
       <c r="M469" t="s" s="2">
-        <v>1223</v>
+        <v>914</v>
       </c>
       <c r="N469" t="s" s="2">
-        <v>1224</v>
-      </c>
-      <c r="O469" t="s" s="2">
-        <v>1225</v>
-      </c>
-      <c r="P469" t="s" s="2">
-        <v>1226</v>
-      </c>
+        <v>915</v>
+      </c>
+      <c r="O469" s="2"/>
+      <c r="P469" s="2"/>
       <c r="Q469" t="s" s="2">
         <v>77</v>
       </c>
@@ -54862,7 +54870,7 @@
         <v>77</v>
       </c>
       <c r="AG469" t="s" s="2">
-        <v>1227</v>
+        <v>916</v>
       </c>
       <c r="AH469" t="s" s="2">
         <v>78</v>
@@ -54874,7 +54882,7 @@
         <v>77</v>
       </c>
       <c r="AK469" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="470">
@@ -54882,10 +54890,10 @@
         <v>1001</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1228</v>
+        <v>1204</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>1229</v>
+        <v>1204</v>
       </c>
       <c r="D470" s="2"/>
       <c r="E470" t="s" s="2">
@@ -54899,24 +54907,26 @@
         <v>86</v>
       </c>
       <c r="I470" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J470" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K470" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L470" t="s" s="2">
-        <v>87</v>
+        <v>333</v>
       </c>
       <c r="M470" t="s" s="2">
-        <v>906</v>
+        <v>919</v>
       </c>
       <c r="N470" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="O470" s="2"/>
+        <v>239</v>
+      </c>
+      <c r="O470" t="s" s="2">
+        <v>1205</v>
+      </c>
       <c r="P470" s="2"/>
       <c r="Q470" t="s" s="2">
         <v>77</v>
@@ -54965,7 +54975,7 @@
         <v>77</v>
       </c>
       <c r="AG470" t="s" s="2">
-        <v>90</v>
+        <v>1204</v>
       </c>
       <c r="AH470" t="s" s="2">
         <v>78</v>
@@ -54977,7 +54987,7 @@
         <v>77</v>
       </c>
       <c r="AK470" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="471">
@@ -54985,10 +54995,10 @@
         <v>1001</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>1230</v>
+        <v>1206</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>1231</v>
+        <v>1206</v>
       </c>
       <c r="D471" s="2"/>
       <c r="E471" t="s" s="2">
@@ -55008,19 +55018,21 @@
         <v>77</v>
       </c>
       <c r="K471" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L471" t="s" s="2">
-        <v>92</v>
+        <v>1207</v>
       </c>
       <c r="M471" t="s" s="2">
-        <v>32</v>
+        <v>1208</v>
       </c>
       <c r="N471" t="s" s="2">
-        <v>82</v>
+        <v>1209</v>
       </c>
       <c r="O471" s="2"/>
-      <c r="P471" s="2"/>
+      <c r="P471" t="s" s="2">
+        <v>1210</v>
+      </c>
       <c r="Q471" t="s" s="2">
         <v>77</v>
       </c>
@@ -55056,17 +55068,19 @@
         <v>77</v>
       </c>
       <c r="AC471" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AD471" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AD471" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AE471" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF471" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG471" t="s" s="2">
-        <v>96</v>
+        <v>1206</v>
       </c>
       <c r="AH471" t="s" s="2">
         <v>78</v>
@@ -55078,7 +55092,7 @@
         <v>77</v>
       </c>
       <c r="AK471" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="472">
@@ -55086,14 +55100,12 @@
         <v>1001</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1232</v>
+        <v>1211</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>1231</v>
-      </c>
-      <c r="D472" t="s" s="2">
-        <v>1233</v>
-      </c>
+        <v>1211</v>
+      </c>
+      <c r="D472" s="2"/>
       <c r="E472" t="s" s="2">
         <v>77</v>
       </c>
@@ -55111,21 +55123,23 @@
         <v>77</v>
       </c>
       <c r="K472" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L472" t="s" s="2">
-        <v>1234</v>
+        <v>1212</v>
       </c>
       <c r="M472" t="s" s="2">
-        <v>1235</v>
+        <v>1213</v>
       </c>
       <c r="N472" t="s" s="2">
-        <v>1236</v>
+        <v>244</v>
       </c>
       <c r="O472" t="s" s="2">
-        <v>1237</v>
-      </c>
-      <c r="P472" s="2"/>
+        <v>1214</v>
+      </c>
+      <c r="P472" t="s" s="2">
+        <v>1215</v>
+      </c>
       <c r="Q472" t="s" s="2">
         <v>77</v>
       </c>
@@ -55161,31 +55175,29 @@
         <v>77</v>
       </c>
       <c r="AC472" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD472" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>1216</v>
+      </c>
+      <c r="AD472" s="2"/>
       <c r="AE472" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF472" t="s" s="2">
-        <v>77</v>
+        <v>1217</v>
       </c>
       <c r="AG472" t="s" s="2">
-        <v>96</v>
+        <v>1211</v>
       </c>
       <c r="AH472" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI472" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ472" t="s" s="2">
-        <v>83</v>
+        <v>1218</v>
       </c>
       <c r="AK472" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="473">
@@ -55193,12 +55205,14 @@
         <v>1001</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>1238</v>
+        <v>1219</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>1239</v>
-      </c>
-      <c r="D473" s="2"/>
+        <v>1211</v>
+      </c>
+      <c r="D473" t="s" s="2">
+        <v>1220</v>
+      </c>
       <c r="E473" t="s" s="2">
         <v>77</v>
       </c>
@@ -55210,25 +55224,29 @@
         <v>86</v>
       </c>
       <c r="I473" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J473" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K473" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L473" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="M473" t="s" s="2">
+        <v>1221</v>
+      </c>
+      <c r="N473" t="s" s="2">
         <v>1222</v>
       </c>
-      <c r="M473" t="s" s="2">
-        <v>1240</v>
-      </c>
-      <c r="N473" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="O473" s="2"/>
-      <c r="P473" s="2"/>
+      <c r="O473" t="s" s="2">
+        <v>1214</v>
+      </c>
+      <c r="P473" t="s" s="2">
+        <v>1215</v>
+      </c>
       <c r="Q473" t="s" s="2">
         <v>77</v>
       </c>
@@ -55276,7 +55294,7 @@
         <v>77</v>
       </c>
       <c r="AG473" t="s" s="2">
-        <v>1241</v>
+        <v>1211</v>
       </c>
       <c r="AH473" t="s" s="2">
         <v>78</v>
@@ -55285,10 +55303,10 @@
         <v>86</v>
       </c>
       <c r="AJ473" t="s" s="2">
-        <v>77</v>
+        <v>1218</v>
       </c>
       <c r="AK473" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="474">
@@ -55296,10 +55314,10 @@
         <v>1001</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>1242</v>
+        <v>1223</v>
       </c>
       <c r="C474" t="s" s="2">
-        <v>1243</v>
+        <v>1224</v>
       </c>
       <c r="D474" s="2"/>
       <c r="E474" t="s" s="2">
@@ -55313,33 +55331,29 @@
         <v>86</v>
       </c>
       <c r="I474" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J474" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K474" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L474" t="s" s="2">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="M474" t="s" s="2">
-        <v>1244</v>
+        <v>88</v>
       </c>
       <c r="N474" t="s" s="2">
-        <v>1245</v>
+        <v>89</v>
       </c>
       <c r="O474" s="2"/>
-      <c r="P474" t="s" s="2">
-        <v>1246</v>
-      </c>
+      <c r="P474" s="2"/>
       <c r="Q474" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="R474" t="s" s="2">
-        <v>1247</v>
-      </c>
+      <c r="R474" s="2"/>
       <c r="S474" t="s" s="2">
         <v>77</v>
       </c>
@@ -55359,13 +55373,13 @@
         <v>77</v>
       </c>
       <c r="Y474" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="Z474" t="s" s="2">
-        <v>1248</v>
+        <v>77</v>
       </c>
       <c r="AA474" t="s" s="2">
-        <v>1249</v>
+        <v>77</v>
       </c>
       <c r="AB474" t="s" s="2">
         <v>77</v>
@@ -55383,7 +55397,7 @@
         <v>77</v>
       </c>
       <c r="AG474" t="s" s="2">
-        <v>1250</v>
+        <v>90</v>
       </c>
       <c r="AH474" t="s" s="2">
         <v>78</v>
@@ -55395,7 +55409,7 @@
         <v>77</v>
       </c>
       <c r="AK474" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="475">
@@ -55403,44 +55417,44 @@
         <v>1001</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>1251</v>
+        <v>1225</v>
       </c>
       <c r="C475" t="s" s="2">
-        <v>1252</v>
+        <v>1226</v>
       </c>
       <c r="D475" s="2"/>
       <c r="E475" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F475" s="2"/>
       <c r="G475" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H475" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I475" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J475" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K475" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L475" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M475" t="s" s="2">
-        <v>1253</v>
+        <v>112</v>
       </c>
       <c r="N475" t="s" s="2">
-        <v>1254</v>
-      </c>
-      <c r="O475" s="2"/>
-      <c r="P475" t="s" s="2">
-        <v>1255</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O475" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="P475" s="2"/>
       <c r="Q475" t="s" s="2">
         <v>77</v>
       </c>
@@ -55476,31 +55490,31 @@
         <v>77</v>
       </c>
       <c r="AC475" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD475" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE475" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF475" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG475" t="s" s="2">
-        <v>1256</v>
+        <v>96</v>
       </c>
       <c r="AH475" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI475" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ475" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK475" t="s" s="2">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="476">
@@ -55508,50 +55522,52 @@
         <v>1001</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>1257</v>
+        <v>1227</v>
       </c>
       <c r="C476" t="s" s="2">
-        <v>1258</v>
-      </c>
-      <c r="D476" s="2"/>
+        <v>1226</v>
+      </c>
+      <c r="D476" t="s" s="2">
+        <v>1228</v>
+      </c>
       <c r="E476" t="s" s="2">
         <v>77</v>
       </c>
       <c r="F476" s="2"/>
       <c r="G476" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H476" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I476" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J476" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K476" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L476" t="s" s="2">
-        <v>98</v>
+        <v>1229</v>
       </c>
       <c r="M476" t="s" s="2">
-        <v>1259</v>
+        <v>1230</v>
       </c>
       <c r="N476" t="s" s="2">
-        <v>1260</v>
-      </c>
-      <c r="O476" s="2"/>
-      <c r="P476" t="s" s="2">
-        <v>1261</v>
-      </c>
+        <v>1231</v>
+      </c>
+      <c r="O476" t="s" s="2">
+        <v>1232</v>
+      </c>
+      <c r="P476" s="2"/>
       <c r="Q476" t="s" s="2">
         <v>77</v>
       </c>
       <c r="R476" s="2"/>
       <c r="S476" t="s" s="2">
-        <v>1262</v>
+        <v>77</v>
       </c>
       <c r="T476" t="s" s="2">
         <v>77</v>
@@ -55593,19 +55609,19 @@
         <v>77</v>
       </c>
       <c r="AG476" t="s" s="2">
-        <v>1263</v>
+        <v>96</v>
       </c>
       <c r="AH476" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI476" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ476" t="s" s="2">
-        <v>1264</v>
+        <v>77</v>
       </c>
       <c r="AK476" t="s" s="2">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="477">
@@ -55613,10 +55629,10 @@
         <v>1001</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>1265</v>
+        <v>1233</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>1266</v>
+        <v>1234</v>
       </c>
       <c r="D477" s="2"/>
       <c r="E477" t="s" s="2">
@@ -55639,19 +55655,19 @@
         <v>80</v>
       </c>
       <c r="L477" t="s" s="2">
-        <v>127</v>
+        <v>1235</v>
       </c>
       <c r="M477" t="s" s="2">
-        <v>1267</v>
+        <v>1236</v>
       </c>
       <c r="N477" t="s" s="2">
-        <v>1268</v>
+        <v>1237</v>
       </c>
       <c r="O477" t="s" s="2">
-        <v>1269</v>
+        <v>1238</v>
       </c>
       <c r="P477" t="s" s="2">
-        <v>1270</v>
+        <v>1239</v>
       </c>
       <c r="Q477" t="s" s="2">
         <v>77</v>
@@ -55700,7 +55716,7 @@
         <v>77</v>
       </c>
       <c r="AG477" t="s" s="2">
-        <v>1271</v>
+        <v>1240</v>
       </c>
       <c r="AH477" t="s" s="2">
         <v>78</v>
@@ -55720,14 +55736,12 @@
         <v>1001</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1272</v>
+        <v>1241</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1198</v>
-      </c>
-      <c r="D478" t="s" s="2">
-        <v>1273</v>
-      </c>
+        <v>1242</v>
+      </c>
+      <c r="D478" s="2"/>
       <c r="E478" t="s" s="2">
         <v>77</v>
       </c>
@@ -55739,29 +55753,25 @@
         <v>86</v>
       </c>
       <c r="I478" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J478" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K478" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L478" t="s" s="2">
-        <v>422</v>
+        <v>87</v>
       </c>
       <c r="M478" t="s" s="2">
-        <v>1208</v>
+        <v>906</v>
       </c>
       <c r="N478" t="s" s="2">
-        <v>1209</v>
-      </c>
-      <c r="O478" t="s" s="2">
-        <v>1201</v>
-      </c>
-      <c r="P478" t="s" s="2">
-        <v>1202</v>
-      </c>
+        <v>907</v>
+      </c>
+      <c r="O478" s="2"/>
+      <c r="P478" s="2"/>
       <c r="Q478" t="s" s="2">
         <v>77</v>
       </c>
@@ -55809,7 +55819,7 @@
         <v>77</v>
       </c>
       <c r="AG478" t="s" s="2">
-        <v>1198</v>
+        <v>90</v>
       </c>
       <c r="AH478" t="s" s="2">
         <v>78</v>
@@ -55818,10 +55828,10 @@
         <v>86</v>
       </c>
       <c r="AJ478" t="s" s="2">
-        <v>1205</v>
+        <v>77</v>
       </c>
       <c r="AK478" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="479">
@@ -55829,10 +55839,10 @@
         <v>1001</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1274</v>
+        <v>1243</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1211</v>
+        <v>1244</v>
       </c>
       <c r="D479" s="2"/>
       <c r="E479" t="s" s="2">
@@ -55843,7 +55853,7 @@
         <v>78</v>
       </c>
       <c r="H479" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I479" t="s" s="2">
         <v>77</v>
@@ -55855,13 +55865,13 @@
         <v>77</v>
       </c>
       <c r="L479" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M479" t="s" s="2">
-        <v>88</v>
+        <v>33</v>
       </c>
       <c r="N479" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="O479" s="2"/>
       <c r="P479" s="2"/>
@@ -55900,31 +55910,29 @@
         <v>77</v>
       </c>
       <c r="AC479" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD479" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="AD479" s="2"/>
       <c r="AE479" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF479" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG479" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AH479" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI479" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ479" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK479" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="480">
@@ -55932,24 +55940,26 @@
         <v>1001</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1275</v>
+        <v>1245</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1213</v>
-      </c>
-      <c r="D480" s="2"/>
+        <v>1244</v>
+      </c>
+      <c r="D480" t="s" s="2">
+        <v>1246</v>
+      </c>
       <c r="E480" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F480" s="2"/>
       <c r="G480" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H480" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I480" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J480" t="s" s="2">
         <v>77</v>
@@ -55958,16 +55968,16 @@
         <v>77</v>
       </c>
       <c r="L480" t="s" s="2">
-        <v>92</v>
+        <v>1247</v>
       </c>
       <c r="M480" t="s" s="2">
-        <v>112</v>
+        <v>1248</v>
       </c>
       <c r="N480" t="s" s="2">
-        <v>113</v>
+        <v>1249</v>
       </c>
       <c r="O480" t="s" s="2">
-        <v>114</v>
+        <v>1250</v>
       </c>
       <c r="P480" s="2"/>
       <c r="Q480" t="s" s="2">
@@ -56005,16 +56015,16 @@
         <v>77</v>
       </c>
       <c r="AC480" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD480" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE480" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF480" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG480" t="s" s="2">
         <v>96</v>
@@ -56026,7 +56036,7 @@
         <v>79</v>
       </c>
       <c r="AJ480" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AK480" t="s" s="2">
         <v>84</v>
@@ -56037,10 +56047,10 @@
         <v>1001</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1276</v>
+        <v>1251</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1277</v>
+        <v>1252</v>
       </c>
       <c r="D481" s="2"/>
       <c r="E481" t="s" s="2">
@@ -56048,35 +56058,31 @@
       </c>
       <c r="F481" s="2"/>
       <c r="G481" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H481" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I481" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J481" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K481" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L481" t="s" s="2">
-        <v>103</v>
+        <v>1235</v>
       </c>
       <c r="M481" t="s" s="2">
-        <v>437</v>
+        <v>1253</v>
       </c>
       <c r="N481" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O481" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="P481" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>915</v>
+      </c>
+      <c r="O481" s="2"/>
+      <c r="P481" s="2"/>
       <c r="Q481" t="s" s="2">
         <v>77</v>
       </c>
@@ -56112,29 +56118,31 @@
         <v>77</v>
       </c>
       <c r="AC481" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="AD481" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AD481" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AE481" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF481" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG481" t="s" s="2">
-        <v>442</v>
+        <v>1254</v>
       </c>
       <c r="AH481" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI481" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ481" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK481" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="482">
@@ -56142,14 +56150,12 @@
         <v>1001</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1278</v>
+        <v>1255</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1277</v>
-      </c>
-      <c r="D482" t="s" s="2">
-        <v>1279</v>
-      </c>
+        <v>1256</v>
+      </c>
+      <c r="D482" s="2"/>
       <c r="E482" t="s" s="2">
         <v>77</v>
       </c>
@@ -56164,30 +56170,30 @@
         <v>80</v>
       </c>
       <c r="J482" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K482" t="s" s="2">
         <v>80</v>
       </c>
       <c r="L482" t="s" s="2">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="M482" t="s" s="2">
-        <v>437</v>
+        <v>1257</v>
       </c>
       <c r="N482" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O482" t="s" s="2">
-        <v>439</v>
-      </c>
+        <v>1258</v>
+      </c>
+      <c r="O482" s="2"/>
       <c r="P482" t="s" s="2">
-        <v>440</v>
+        <v>1259</v>
       </c>
       <c r="Q482" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="R482" s="2"/>
+      <c r="R482" t="s" s="2">
+        <v>1260</v>
+      </c>
       <c r="S482" t="s" s="2">
         <v>77</v>
       </c>
@@ -56209,9 +56215,11 @@
       <c r="Y482" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="Z482" s="2"/>
+      <c r="Z482" t="s" s="2">
+        <v>1261</v>
+      </c>
       <c r="AA482" t="s" s="2">
-        <v>1280</v>
+        <v>1262</v>
       </c>
       <c r="AB482" t="s" s="2">
         <v>77</v>
@@ -56229,13 +56237,13 @@
         <v>77</v>
       </c>
       <c r="AG482" t="s" s="2">
-        <v>442</v>
+        <v>1263</v>
       </c>
       <c r="AH482" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI482" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ482" t="s" s="2">
         <v>77</v>
@@ -56249,10 +56257,10 @@
         <v>1001</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1281</v>
+        <v>1264</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1282</v>
+        <v>1265</v>
       </c>
       <c r="D483" s="2"/>
       <c r="E483" t="s" s="2">
@@ -56260,31 +56268,33 @@
       </c>
       <c r="F483" s="2"/>
       <c r="G483" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H483" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I483" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J483" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K483" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L483" t="s" s="2">
         <v>87</v>
       </c>
       <c r="M483" t="s" s="2">
-        <v>88</v>
+        <v>1266</v>
       </c>
       <c r="N483" t="s" s="2">
-        <v>89</v>
+        <v>1267</v>
       </c>
       <c r="O483" s="2"/>
-      <c r="P483" s="2"/>
+      <c r="P483" t="s" s="2">
+        <v>1268</v>
+      </c>
       <c r="Q483" t="s" s="2">
         <v>77</v>
       </c>
@@ -56332,7 +56342,7 @@
         <v>77</v>
       </c>
       <c r="AG483" t="s" s="2">
-        <v>90</v>
+        <v>1269</v>
       </c>
       <c r="AH483" t="s" s="2">
         <v>78</v>
@@ -56344,7 +56354,7 @@
         <v>77</v>
       </c>
       <c r="AK483" t="s" s="2">
-        <v>77</v>
+        <v>108</v>
       </c>
     </row>
     <row r="484">
@@ -56352,50 +56362,50 @@
         <v>1001</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1283</v>
+        <v>1270</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1284</v>
+        <v>1271</v>
       </c>
       <c r="D484" s="2"/>
       <c r="E484" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F484" s="2"/>
       <c r="G484" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H484" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I484" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J484" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K484" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L484" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="M484" t="s" s="2">
-        <v>112</v>
+        <v>1272</v>
       </c>
       <c r="N484" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O484" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="P484" s="2"/>
+        <v>1273</v>
+      </c>
+      <c r="O484" s="2"/>
+      <c r="P484" t="s" s="2">
+        <v>1274</v>
+      </c>
       <c r="Q484" t="s" s="2">
         <v>77</v>
       </c>
       <c r="R484" s="2"/>
       <c r="S484" t="s" s="2">
-        <v>77</v>
+        <v>1275</v>
       </c>
       <c r="T484" t="s" s="2">
         <v>77</v>
@@ -56425,31 +56435,31 @@
         <v>77</v>
       </c>
       <c r="AC484" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD484" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE484" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF484" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG484" t="s" s="2">
-        <v>96</v>
+        <v>1276</v>
       </c>
       <c r="AH484" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI484" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ484" t="s" s="2">
-        <v>77</v>
+        <v>1277</v>
       </c>
       <c r="AK484" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="485">
@@ -56457,10 +56467,10 @@
         <v>1001</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1285</v>
+        <v>1278</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1286</v>
+        <v>1279</v>
       </c>
       <c r="D485" s="2"/>
       <c r="E485" t="s" s="2">
@@ -56468,7 +56478,7 @@
       </c>
       <c r="F485" s="2"/>
       <c r="G485" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H485" t="s" s="2">
         <v>86</v>
@@ -56483,19 +56493,19 @@
         <v>80</v>
       </c>
       <c r="L485" t="s" s="2">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="M485" t="s" s="2">
-        <v>116</v>
+        <v>1280</v>
       </c>
       <c r="N485" t="s" s="2">
-        <v>117</v>
+        <v>1281</v>
       </c>
       <c r="O485" t="s" s="2">
-        <v>118</v>
+        <v>1282</v>
       </c>
       <c r="P485" t="s" s="2">
-        <v>119</v>
+        <v>1283</v>
       </c>
       <c r="Q485" t="s" s="2">
         <v>77</v>
@@ -56544,7 +56554,7 @@
         <v>77</v>
       </c>
       <c r="AG485" t="s" s="2">
-        <v>120</v>
+        <v>1284</v>
       </c>
       <c r="AH485" t="s" s="2">
         <v>78</v>
@@ -56564,12 +56574,14 @@
         <v>1001</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1288</v>
-      </c>
-      <c r="D486" s="2"/>
+        <v>1211</v>
+      </c>
+      <c r="D486" t="s" s="2">
+        <v>1286</v>
+      </c>
       <c r="E486" t="s" s="2">
         <v>77</v>
       </c>
@@ -56581,7 +56593,7 @@
         <v>86</v>
       </c>
       <c r="I486" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J486" t="s" s="2">
         <v>77</v>
@@ -56590,18 +56602,20 @@
         <v>80</v>
       </c>
       <c r="L486" t="s" s="2">
-        <v>87</v>
+        <v>422</v>
       </c>
       <c r="M486" t="s" s="2">
-        <v>122</v>
+        <v>1221</v>
       </c>
       <c r="N486" t="s" s="2">
-        <v>123</v>
+        <v>1222</v>
       </c>
       <c r="O486" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="P486" s="2"/>
+        <v>1214</v>
+      </c>
+      <c r="P486" t="s" s="2">
+        <v>1215</v>
+      </c>
       <c r="Q486" t="s" s="2">
         <v>77</v>
       </c>
@@ -56625,13 +56639,11 @@
         <v>77</v>
       </c>
       <c r="Y486" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z486" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="Z486" s="2"/>
       <c r="AA486" t="s" s="2">
-        <v>77</v>
+        <v>1287</v>
       </c>
       <c r="AB486" t="s" s="2">
         <v>77</v>
@@ -56649,7 +56661,7 @@
         <v>77</v>
       </c>
       <c r="AG486" t="s" s="2">
-        <v>125</v>
+        <v>1211</v>
       </c>
       <c r="AH486" t="s" s="2">
         <v>78</v>
@@ -56658,7 +56670,7 @@
         <v>86</v>
       </c>
       <c r="AJ486" t="s" s="2">
-        <v>77</v>
+        <v>1218</v>
       </c>
       <c r="AK486" t="s" s="2">
         <v>108</v>
@@ -56669,10 +56681,10 @@
         <v>1001</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1290</v>
+        <v>1224</v>
       </c>
       <c r="D487" s="2"/>
       <c r="E487" t="s" s="2">
@@ -56686,27 +56698,25 @@
         <v>86</v>
       </c>
       <c r="I487" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J487" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K487" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L487" t="s" s="2">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="M487" t="s" s="2">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="N487" t="s" s="2">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="O487" s="2"/>
-      <c r="P487" t="s" s="2">
-        <v>130</v>
-      </c>
+      <c r="P487" s="2"/>
       <c r="Q487" t="s" s="2">
         <v>77</v>
       </c>
@@ -56754,7 +56764,7 @@
         <v>77</v>
       </c>
       <c r="AG487" t="s" s="2">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="AH487" t="s" s="2">
         <v>78</v>
@@ -56766,7 +56776,7 @@
         <v>77</v>
       </c>
       <c r="AK487" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="488">
@@ -56774,21 +56784,21 @@
         <v>1001</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1292</v>
+        <v>1226</v>
       </c>
       <c r="D488" s="2"/>
       <c r="E488" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F488" s="2"/>
       <c r="G488" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H488" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I488" t="s" s="2">
         <v>77</v>
@@ -56797,21 +56807,21 @@
         <v>77</v>
       </c>
       <c r="K488" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L488" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M488" t="s" s="2">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="N488" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O488" s="2"/>
-      <c r="P488" t="s" s="2">
-        <v>135</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="O488" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="P488" s="2"/>
       <c r="Q488" t="s" s="2">
         <v>77</v>
       </c>
@@ -56847,31 +56857,31 @@
         <v>77</v>
       </c>
       <c r="AC488" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD488" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE488" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF488" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG488" t="s" s="2">
-        <v>136</v>
+        <v>96</v>
       </c>
       <c r="AH488" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI488" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ488" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK488" t="s" s="2">
-        <v>108</v>
+        <v>84</v>
       </c>
     </row>
     <row r="489">
@@ -56879,10 +56889,10 @@
         <v>1001</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1293</v>
+        <v>1290</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1294</v>
+        <v>1291</v>
       </c>
       <c r="D489" s="2"/>
       <c r="E489" t="s" s="2">
@@ -56890,13 +56900,13 @@
       </c>
       <c r="F489" s="2"/>
       <c r="G489" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H489" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I489" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J489" t="s" s="2">
         <v>77</v>
@@ -56905,19 +56915,19 @@
         <v>80</v>
       </c>
       <c r="L489" t="s" s="2">
-        <v>138</v>
+        <v>103</v>
       </c>
       <c r="M489" t="s" s="2">
-        <v>139</v>
+        <v>437</v>
       </c>
       <c r="N489" t="s" s="2">
-        <v>140</v>
+        <v>438</v>
       </c>
       <c r="O489" t="s" s="2">
-        <v>141</v>
+        <v>439</v>
       </c>
       <c r="P489" t="s" s="2">
-        <v>142</v>
+        <v>440</v>
       </c>
       <c r="Q489" t="s" s="2">
         <v>77</v>
@@ -56966,13 +56976,13 @@
         <v>77</v>
       </c>
       <c r="AG489" t="s" s="2">
-        <v>143</v>
+        <v>442</v>
       </c>
       <c r="AH489" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI489" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ489" t="s" s="2">
         <v>77</v>
@@ -56986,14 +56996,12 @@
         <v>1001</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1295</v>
+        <v>1292</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1277</v>
-      </c>
-      <c r="D490" t="s" s="2">
-        <v>1296</v>
-      </c>
+        <v>1293</v>
+      </c>
+      <c r="D490" s="2"/>
       <c r="E490" t="s" s="2">
         <v>77</v>
       </c>
@@ -57005,29 +57013,25 @@
         <v>86</v>
       </c>
       <c r="I490" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J490" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K490" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L490" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="M490" t="s" s="2">
-        <v>437</v>
+        <v>88</v>
       </c>
       <c r="N490" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O490" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="P490" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O490" s="2"/>
+      <c r="P490" s="2"/>
       <c r="Q490" t="s" s="2">
         <v>77</v>
       </c>
@@ -57051,11 +57055,13 @@
         <v>77</v>
       </c>
       <c r="Y490" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Z490" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Z490" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AA490" t="s" s="2">
-        <v>1297</v>
+        <v>77</v>
       </c>
       <c r="AB490" t="s" s="2">
         <v>77</v>
@@ -57073,19 +57079,19 @@
         <v>77</v>
       </c>
       <c r="AG490" t="s" s="2">
-        <v>442</v>
+        <v>90</v>
       </c>
       <c r="AH490" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI490" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ490" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK490" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="491">
@@ -57093,21 +57099,21 @@
         <v>1001</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1282</v>
+        <v>1295</v>
       </c>
       <c r="D491" s="2"/>
       <c r="E491" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F491" s="2"/>
       <c r="G491" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H491" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I491" t="s" s="2">
         <v>77</v>
@@ -57119,15 +57125,17 @@
         <v>77</v>
       </c>
       <c r="L491" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M491" t="s" s="2">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="N491" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O491" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O491" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P491" s="2"/>
       <c r="Q491" t="s" s="2">
         <v>77</v>
@@ -57164,31 +57172,31 @@
         <v>77</v>
       </c>
       <c r="AC491" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD491" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE491" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF491" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG491" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AH491" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI491" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ491" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK491" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="492">
@@ -57196,44 +57204,46 @@
         <v>1001</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1284</v>
+        <v>1297</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F492" s="2"/>
       <c r="G492" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H492" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I492" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J492" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K492" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L492" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="M492" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="N492" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="O492" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="P492" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="P492" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="Q492" t="s" s="2">
         <v>77</v>
       </c>
@@ -57269,31 +57279,31 @@
         <v>77</v>
       </c>
       <c r="AC492" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD492" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE492" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF492" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG492" t="s" s="2">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="AH492" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI492" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ492" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK492" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="493">
@@ -57301,10 +57311,10 @@
         <v>1001</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1286</v>
+        <v>1299</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -57327,20 +57337,18 @@
         <v>80</v>
       </c>
       <c r="L493" t="s" s="2">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="N493" t="s" s="2">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="O493" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="P493" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="P493" s="2"/>
       <c r="Q493" t="s" s="2">
         <v>77</v>
       </c>
@@ -57388,7 +57396,7 @@
         <v>77</v>
       </c>
       <c r="AG493" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AH493" t="s" s="2">
         <v>78</v>
@@ -57408,10 +57416,10 @@
         <v>1001</v>
       </c>
       <c r="B494" t="s" s="2">
+        <v>1300</v>
+      </c>
+      <c r="C494" t="s" s="2">
         <v>1301</v>
-      </c>
-      <c r="C494" t="s" s="2">
-        <v>1288</v>
       </c>
       <c r="D494" s="2"/>
       <c r="E494" t="s" s="2">
@@ -57419,13 +57427,13 @@
       </c>
       <c r="F494" s="2"/>
       <c r="G494" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H494" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I494" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J494" t="s" s="2">
         <v>77</v>
@@ -57434,18 +57442,18 @@
         <v>80</v>
       </c>
       <c r="L494" t="s" s="2">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="M494" t="s" s="2">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="N494" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="O494" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="P494" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="O494" s="2"/>
+      <c r="P494" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="Q494" t="s" s="2">
         <v>77</v>
       </c>
@@ -57493,7 +57501,7 @@
         <v>77</v>
       </c>
       <c r="AG494" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AH494" t="s" s="2">
         <v>78</v>
@@ -57516,7 +57524,7 @@
         <v>1302</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1290</v>
+        <v>1303</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
@@ -57530,7 +57538,7 @@
         <v>86</v>
       </c>
       <c r="I495" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J495" t="s" s="2">
         <v>77</v>
@@ -57539,17 +57547,17 @@
         <v>80</v>
       </c>
       <c r="L495" t="s" s="2">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="M495" t="s" s="2">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="N495" t="s" s="2">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="O495" s="2"/>
       <c r="P495" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="Q495" t="s" s="2">
         <v>77</v>
@@ -57598,7 +57606,7 @@
         <v>77</v>
       </c>
       <c r="AG495" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="AH495" t="s" s="2">
         <v>78</v>
@@ -57618,10 +57626,10 @@
         <v>1001</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1292</v>
+        <v>1305</v>
       </c>
       <c r="D496" s="2"/>
       <c r="E496" t="s" s="2">
@@ -57644,17 +57652,19 @@
         <v>80</v>
       </c>
       <c r="L496" t="s" s="2">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="M496" t="s" s="2">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="N496" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O496" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O496" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P496" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="Q496" t="s" s="2">
         <v>77</v>
@@ -57703,7 +57713,7 @@
         <v>77</v>
       </c>
       <c r="AG496" t="s" s="2">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="AH496" t="s" s="2">
         <v>78</v>
@@ -57723,10 +57733,10 @@
         <v>1001</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1294</v>
+        <v>1307</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" t="s" s="2">
@@ -57749,19 +57759,19 @@
         <v>80</v>
       </c>
       <c r="L497" t="s" s="2">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="M497" t="s" s="2">
-        <v>139</v>
+        <v>463</v>
       </c>
       <c r="N497" t="s" s="2">
-        <v>140</v>
+        <v>464</v>
       </c>
       <c r="O497" t="s" s="2">
-        <v>141</v>
+        <v>465</v>
       </c>
       <c r="P497" t="s" s="2">
-        <v>142</v>
+        <v>466</v>
       </c>
       <c r="Q497" t="s" s="2">
         <v>77</v>
@@ -57810,7 +57820,7 @@
         <v>77</v>
       </c>
       <c r="AG497" t="s" s="2">
-        <v>143</v>
+        <v>467</v>
       </c>
       <c r="AH497" t="s" s="2">
         <v>78</v>
@@ -57830,12 +57840,14 @@
         <v>1001</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1305</v>
+        <v>1308</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1306</v>
-      </c>
-      <c r="D498" s="2"/>
+        <v>1211</v>
+      </c>
+      <c r="D498" t="s" s="2">
+        <v>1309</v>
+      </c>
       <c r="E498" t="s" s="2">
         <v>77</v>
       </c>
@@ -57847,7 +57859,7 @@
         <v>86</v>
       </c>
       <c r="I498" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J498" t="s" s="2">
         <v>77</v>
@@ -57856,19 +57868,19 @@
         <v>80</v>
       </c>
       <c r="L498" t="s" s="2">
-        <v>87</v>
+        <v>1310</v>
       </c>
       <c r="M498" t="s" s="2">
-        <v>463</v>
+        <v>1221</v>
       </c>
       <c r="N498" t="s" s="2">
-        <v>464</v>
+        <v>1222</v>
       </c>
       <c r="O498" t="s" s="2">
-        <v>465</v>
+        <v>1214</v>
       </c>
       <c r="P498" t="s" s="2">
-        <v>466</v>
+        <v>1215</v>
       </c>
       <c r="Q498" t="s" s="2">
         <v>77</v>
@@ -57917,7 +57929,7 @@
         <v>77</v>
       </c>
       <c r="AG498" t="s" s="2">
-        <v>467</v>
+        <v>1211</v>
       </c>
       <c r="AH498" t="s" s="2">
         <v>78</v>
@@ -57926,7 +57938,7 @@
         <v>86</v>
       </c>
       <c r="AJ498" t="s" s="2">
-        <v>77</v>
+        <v>1218</v>
       </c>
       <c r="AK498" t="s" s="2">
         <v>108</v>
@@ -57937,13 +57949,13 @@
         <v>1001</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1307</v>
+        <v>1311</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="D499" t="s" s="2">
-        <v>1308</v>
+        <v>1312</v>
       </c>
       <c r="E499" t="s" s="2">
         <v>77</v>
@@ -57965,19 +57977,19 @@
         <v>80</v>
       </c>
       <c r="L499" t="s" s="2">
-        <v>1309</v>
+        <v>1313</v>
       </c>
       <c r="M499" t="s" s="2">
-        <v>1208</v>
+        <v>1221</v>
       </c>
       <c r="N499" t="s" s="2">
-        <v>1209</v>
+        <v>1222</v>
       </c>
       <c r="O499" t="s" s="2">
-        <v>1201</v>
+        <v>1214</v>
       </c>
       <c r="P499" t="s" s="2">
-        <v>1202</v>
+        <v>1215</v>
       </c>
       <c r="Q499" t="s" s="2">
         <v>77</v>
@@ -58026,7 +58038,7 @@
         <v>77</v>
       </c>
       <c r="AG499" t="s" s="2">
-        <v>1198</v>
+        <v>1211</v>
       </c>
       <c r="AH499" t="s" s="2">
         <v>78</v>
@@ -58035,7 +58047,7 @@
         <v>86</v>
       </c>
       <c r="AJ499" t="s" s="2">
-        <v>1205</v>
+        <v>1218</v>
       </c>
       <c r="AK499" t="s" s="2">
         <v>108</v>
@@ -58046,14 +58058,12 @@
         <v>1001</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1310</v>
+        <v>1314</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1198</v>
-      </c>
-      <c r="D500" t="s" s="2">
-        <v>1311</v>
-      </c>
+        <v>1314</v>
+      </c>
+      <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
         <v>77</v>
       </c>
@@ -58071,22 +58081,22 @@
         <v>77</v>
       </c>
       <c r="K500" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L500" t="s" s="2">
-        <v>1312</v>
+        <v>422</v>
       </c>
       <c r="M500" t="s" s="2">
-        <v>1208</v>
+        <v>1315</v>
       </c>
       <c r="N500" t="s" s="2">
-        <v>1209</v>
+        <v>1316</v>
       </c>
       <c r="O500" t="s" s="2">
-        <v>1201</v>
+        <v>1317</v>
       </c>
       <c r="P500" t="s" s="2">
-        <v>1202</v>
+        <v>1318</v>
       </c>
       <c r="Q500" t="s" s="2">
         <v>77</v>
@@ -58111,13 +58121,13 @@
         <v>77</v>
       </c>
       <c r="Y500" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="Z500" t="s" s="2">
-        <v>77</v>
+        <v>1319</v>
       </c>
       <c r="AA500" t="s" s="2">
-        <v>77</v>
+        <v>1320</v>
       </c>
       <c r="AB500" t="s" s="2">
         <v>77</v>
@@ -58135,7 +58145,7 @@
         <v>77</v>
       </c>
       <c r="AG500" t="s" s="2">
-        <v>1198</v>
+        <v>1314</v>
       </c>
       <c r="AH500" t="s" s="2">
         <v>78</v>
@@ -58144,7 +58154,7 @@
         <v>86</v>
       </c>
       <c r="AJ500" t="s" s="2">
-        <v>1205</v>
+        <v>1321</v>
       </c>
       <c r="AK500" t="s" s="2">
         <v>108</v>
@@ -58155,21 +58165,21 @@
         <v>1001</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1313</v>
+        <v>1322</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1313</v>
+        <v>1322</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
-        <v>77</v>
+        <v>1323</v>
       </c>
       <c r="F501" s="2"/>
       <c r="G501" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H501" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I501" t="s" s="2">
         <v>80</v>
@@ -58184,16 +58194,16 @@
         <v>422</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>1314</v>
+        <v>1324</v>
       </c>
       <c r="N501" t="s" s="2">
-        <v>1315</v>
+        <v>1325</v>
       </c>
       <c r="O501" t="s" s="2">
-        <v>1316</v>
+        <v>1326</v>
       </c>
       <c r="P501" t="s" s="2">
-        <v>1317</v>
+        <v>1327</v>
       </c>
       <c r="Q501" t="s" s="2">
         <v>77</v>
@@ -58221,10 +58231,10 @@
         <v>106</v>
       </c>
       <c r="Z501" t="s" s="2">
-        <v>1318</v>
+        <v>1328</v>
       </c>
       <c r="AA501" t="s" s="2">
-        <v>1319</v>
+        <v>1329</v>
       </c>
       <c r="AB501" t="s" s="2">
         <v>77</v>
@@ -58242,16 +58252,16 @@
         <v>77</v>
       </c>
       <c r="AG501" t="s" s="2">
-        <v>1313</v>
+        <v>1322</v>
       </c>
       <c r="AH501" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI501" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ501" t="s" s="2">
-        <v>1320</v>
+        <v>77</v>
       </c>
       <c r="AK501" t="s" s="2">
         <v>108</v>
@@ -58262,14 +58272,14 @@
         <v>1001</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1321</v>
+        <v>1330</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1321</v>
+        <v>1330</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
-        <v>1322</v>
+        <v>77</v>
       </c>
       <c r="F502" s="2"/>
       <c r="G502" t="s" s="2">
@@ -58288,19 +58298,19 @@
         <v>77</v>
       </c>
       <c r="L502" t="s" s="2">
-        <v>422</v>
+        <v>727</v>
       </c>
       <c r="M502" t="s" s="2">
-        <v>1323</v>
+        <v>1331</v>
       </c>
       <c r="N502" t="s" s="2">
-        <v>1324</v>
+        <v>1332</v>
       </c>
       <c r="O502" t="s" s="2">
-        <v>1325</v>
+        <v>1333</v>
       </c>
       <c r="P502" t="s" s="2">
-        <v>1326</v>
+        <v>1334</v>
       </c>
       <c r="Q502" t="s" s="2">
         <v>77</v>
@@ -58325,13 +58335,13 @@
         <v>77</v>
       </c>
       <c r="Y502" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="Z502" t="s" s="2">
-        <v>1327</v>
+        <v>77</v>
       </c>
       <c r="AA502" t="s" s="2">
-        <v>1328</v>
+        <v>77</v>
       </c>
       <c r="AB502" t="s" s="2">
         <v>77</v>
@@ -58349,7 +58359,7 @@
         <v>77</v>
       </c>
       <c r="AG502" t="s" s="2">
-        <v>1321</v>
+        <v>1330</v>
       </c>
       <c r="AH502" t="s" s="2">
         <v>78</v>
@@ -58369,10 +58379,10 @@
         <v>1001</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
@@ -58383,10 +58393,10 @@
         <v>78</v>
       </c>
       <c r="H503" t="s" s="2">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I503" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J503" t="s" s="2">
         <v>77</v>
@@ -58395,20 +58405,18 @@
         <v>77</v>
       </c>
       <c r="L503" t="s" s="2">
-        <v>727</v>
+        <v>422</v>
       </c>
       <c r="M503" t="s" s="2">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="N503" t="s" s="2">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="O503" t="s" s="2">
-        <v>1332</v>
-      </c>
-      <c r="P503" t="s" s="2">
-        <v>1333</v>
-      </c>
+        <v>1338</v>
+      </c>
+      <c r="P503" s="2"/>
       <c r="Q503" t="s" s="2">
         <v>77</v>
       </c>
@@ -58432,13 +58440,13 @@
         <v>77</v>
       </c>
       <c r="Y503" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="Z503" t="s" s="2">
-        <v>77</v>
+        <v>724</v>
       </c>
       <c r="AA503" t="s" s="2">
-        <v>77</v>
+        <v>725</v>
       </c>
       <c r="AB503" t="s" s="2">
         <v>77</v>
@@ -58456,13 +58464,13 @@
         <v>77</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="AH503" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI503" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ503" t="s" s="2">
         <v>77</v>
@@ -58476,10 +58484,10 @@
         <v>1001</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
@@ -58490,10 +58498,10 @@
         <v>78</v>
       </c>
       <c r="H504" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I504" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J504" t="s" s="2">
         <v>77</v>
@@ -58505,15 +58513,17 @@
         <v>422</v>
       </c>
       <c r="M504" t="s" s="2">
-        <v>1335</v>
+        <v>1340</v>
       </c>
       <c r="N504" t="s" s="2">
-        <v>1336</v>
+        <v>1341</v>
       </c>
       <c r="O504" t="s" s="2">
-        <v>1337</v>
-      </c>
-      <c r="P504" s="2"/>
+        <v>1342</v>
+      </c>
+      <c r="P504" t="s" s="2">
+        <v>1343</v>
+      </c>
       <c r="Q504" t="s" s="2">
         <v>77</v>
       </c>
@@ -58540,10 +58550,10 @@
         <v>360</v>
       </c>
       <c r="Z504" t="s" s="2">
-        <v>724</v>
+        <v>1344</v>
       </c>
       <c r="AA504" t="s" s="2">
-        <v>725</v>
+        <v>1345</v>
       </c>
       <c r="AB504" t="s" s="2">
         <v>77</v>
@@ -58561,7 +58571,7 @@
         <v>77</v>
       </c>
       <c r="AG504" t="s" s="2">
-        <v>1334</v>
+        <v>1339</v>
       </c>
       <c r="AH504" t="s" s="2">
         <v>78</v>
@@ -58581,10 +58591,10 @@
         <v>1001</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1338</v>
+        <v>1346</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1338</v>
+        <v>1346</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" t="s" s="2">
@@ -58598,7 +58608,7 @@
         <v>86</v>
       </c>
       <c r="I505" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J505" t="s" s="2">
         <v>77</v>
@@ -58607,20 +58617,16 @@
         <v>77</v>
       </c>
       <c r="L505" t="s" s="2">
-        <v>422</v>
+        <v>87</v>
       </c>
       <c r="M505" t="s" s="2">
-        <v>1339</v>
+        <v>88</v>
       </c>
       <c r="N505" t="s" s="2">
-        <v>1340</v>
-      </c>
-      <c r="O505" t="s" s="2">
-        <v>1341</v>
-      </c>
-      <c r="P505" t="s" s="2">
-        <v>1342</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O505" s="2"/>
+      <c r="P505" s="2"/>
       <c r="Q505" t="s" s="2">
         <v>77</v>
       </c>
@@ -58644,13 +58650,13 @@
         <v>77</v>
       </c>
       <c r="Y505" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="Z505" t="s" s="2">
-        <v>1343</v>
+        <v>77</v>
       </c>
       <c r="AA505" t="s" s="2">
-        <v>1344</v>
+        <v>77</v>
       </c>
       <c r="AB505" t="s" s="2">
         <v>77</v>
@@ -58668,7 +58674,7 @@
         <v>77</v>
       </c>
       <c r="AG505" t="s" s="2">
-        <v>1338</v>
+        <v>90</v>
       </c>
       <c r="AH505" t="s" s="2">
         <v>78</v>
@@ -58680,7 +58686,7 @@
         <v>77</v>
       </c>
       <c r="AK505" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="506">
@@ -58688,21 +58694,21 @@
         <v>1001</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F506" s="2"/>
       <c r="G506" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H506" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I506" t="s" s="2">
         <v>77</v>
@@ -58714,15 +58720,17 @@
         <v>77</v>
       </c>
       <c r="L506" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M506" t="s" s="2">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="N506" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O506" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O506" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P506" s="2"/>
       <c r="Q506" t="s" s="2">
         <v>77</v>
@@ -58759,31 +58767,31 @@
         <v>77</v>
       </c>
       <c r="AC506" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD506" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE506" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF506" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG506" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AH506" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI506" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ506" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK506" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="507">
@@ -58791,14 +58799,14 @@
         <v>1001</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F507" s="2"/>
       <c r="G507" t="s" s="2">
@@ -58808,27 +58816,29 @@
         <v>79</v>
       </c>
       <c r="I507" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J507" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K507" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L507" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="M507" t="s" s="2">
-        <v>112</v>
+        <v>437</v>
       </c>
       <c r="N507" t="s" s="2">
-        <v>113</v>
+        <v>438</v>
       </c>
       <c r="O507" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="P507" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="P507" t="s" s="2">
+        <v>440</v>
+      </c>
       <c r="Q507" t="s" s="2">
         <v>77</v>
       </c>
@@ -58864,19 +58874,19 @@
         <v>77</v>
       </c>
       <c r="AC507" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD507" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE507" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF507" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG507" t="s" s="2">
-        <v>96</v>
+        <v>442</v>
       </c>
       <c r="AH507" t="s" s="2">
         <v>78</v>
@@ -58888,7 +58898,7 @@
         <v>77</v>
       </c>
       <c r="AK507" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="508">
@@ -58896,10 +58906,10 @@
         <v>1001</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -58910,32 +58920,28 @@
         <v>78</v>
       </c>
       <c r="H508" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I508" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J508" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K508" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L508" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="M508" t="s" s="2">
-        <v>437</v>
+        <v>88</v>
       </c>
       <c r="N508" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O508" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="P508" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O508" s="2"/>
+      <c r="P508" s="2"/>
       <c r="Q508" t="s" s="2">
         <v>77</v>
       </c>
@@ -58983,19 +58989,19 @@
         <v>77</v>
       </c>
       <c r="AG508" t="s" s="2">
-        <v>442</v>
+        <v>90</v>
       </c>
       <c r="AH508" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI508" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ508" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK508" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="509">
@@ -59003,21 +59009,21 @@
         <v>1001</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F509" s="2"/>
       <c r="G509" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H509" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I509" t="s" s="2">
         <v>77</v>
@@ -59029,15 +59035,17 @@
         <v>77</v>
       </c>
       <c r="L509" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M509" t="s" s="2">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="N509" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O509" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O509" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P509" s="2"/>
       <c r="Q509" t="s" s="2">
         <v>77</v>
@@ -59074,31 +59082,31 @@
         <v>77</v>
       </c>
       <c r="AC509" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD509" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE509" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF509" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG509" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AH509" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI509" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ509" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK509" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="510">
@@ -59106,44 +59114,46 @@
         <v>1001</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F510" s="2"/>
       <c r="G510" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H510" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I510" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J510" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K510" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L510" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="M510" t="s" s="2">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="N510" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="O510" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="P510" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="P510" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="Q510" t="s" s="2">
         <v>77</v>
       </c>
@@ -59179,31 +59189,31 @@
         <v>77</v>
       </c>
       <c r="AC510" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD510" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE510" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF510" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG510" t="s" s="2">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="AH510" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI510" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ510" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK510" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="511">
@@ -59211,10 +59221,10 @@
         <v>1001</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -59222,13 +59232,13 @@
       </c>
       <c r="F511" s="2"/>
       <c r="G511" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H511" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I511" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J511" t="s" s="2">
         <v>77</v>
@@ -59237,20 +59247,18 @@
         <v>80</v>
       </c>
       <c r="L511" t="s" s="2">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="M511" t="s" s="2">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="N511" t="s" s="2">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="O511" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="P511" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="P511" s="2"/>
       <c r="Q511" t="s" s="2">
         <v>77</v>
       </c>
@@ -59298,7 +59306,7 @@
         <v>77</v>
       </c>
       <c r="AG511" t="s" s="2">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AH511" t="s" s="2">
         <v>78</v>
@@ -59318,10 +59326,10 @@
         <v>1001</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -59329,13 +59337,13 @@
       </c>
       <c r="F512" s="2"/>
       <c r="G512" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H512" t="s" s="2">
         <v>86</v>
       </c>
       <c r="I512" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J512" t="s" s="2">
         <v>77</v>
@@ -59344,18 +59352,18 @@
         <v>80</v>
       </c>
       <c r="L512" t="s" s="2">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="M512" t="s" s="2">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="N512" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="O512" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="P512" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="O512" s="2"/>
+      <c r="P512" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="Q512" t="s" s="2">
         <v>77</v>
       </c>
@@ -59403,7 +59411,7 @@
         <v>77</v>
       </c>
       <c r="AG512" t="s" s="2">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="AH512" t="s" s="2">
         <v>78</v>
@@ -59423,10 +59431,10 @@
         <v>1001</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
@@ -59434,7 +59442,7 @@
       </c>
       <c r="F513" s="2"/>
       <c r="G513" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H513" t="s" s="2">
         <v>86</v>
@@ -59449,17 +59457,17 @@
         <v>80</v>
       </c>
       <c r="L513" t="s" s="2">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="M513" t="s" s="2">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="N513" t="s" s="2">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="O513" s="2"/>
       <c r="P513" t="s" s="2">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="Q513" t="s" s="2">
         <v>77</v>
@@ -59508,7 +59516,7 @@
         <v>77</v>
       </c>
       <c r="AG513" t="s" s="2">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="AH513" t="s" s="2">
         <v>78</v>
@@ -59528,10 +59536,10 @@
         <v>1001</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
@@ -59545,7 +59553,7 @@
         <v>86</v>
       </c>
       <c r="I514" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J514" t="s" s="2">
         <v>77</v>
@@ -59554,17 +59562,19 @@
         <v>80</v>
       </c>
       <c r="L514" t="s" s="2">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="M514" t="s" s="2">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="N514" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="O514" s="2"/>
+        <v>140</v>
+      </c>
+      <c r="O514" t="s" s="2">
+        <v>141</v>
+      </c>
       <c r="P514" t="s" s="2">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="Q514" t="s" s="2">
         <v>77</v>
@@ -59613,7 +59623,7 @@
         <v>77</v>
       </c>
       <c r="AG514" t="s" s="2">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="AH514" t="s" s="2">
         <v>78</v>
@@ -59633,10 +59643,10 @@
         <v>1001</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -59659,19 +59669,19 @@
         <v>80</v>
       </c>
       <c r="L515" t="s" s="2">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="M515" t="s" s="2">
-        <v>139</v>
+        <v>463</v>
       </c>
       <c r="N515" t="s" s="2">
-        <v>140</v>
+        <v>464</v>
       </c>
       <c r="O515" t="s" s="2">
-        <v>141</v>
+        <v>465</v>
       </c>
       <c r="P515" t="s" s="2">
-        <v>142</v>
+        <v>466</v>
       </c>
       <c r="Q515" t="s" s="2">
         <v>77</v>
@@ -59720,7 +59730,7 @@
         <v>77</v>
       </c>
       <c r="AG515" t="s" s="2">
-        <v>143</v>
+        <v>467</v>
       </c>
       <c r="AH515" t="s" s="2">
         <v>78</v>
@@ -59740,10 +59750,10 @@
         <v>1001</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
@@ -59757,29 +59767,27 @@
         <v>86</v>
       </c>
       <c r="I516" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J516" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K516" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L516" t="s" s="2">
-        <v>87</v>
+        <v>708</v>
       </c>
       <c r="M516" t="s" s="2">
-        <v>463</v>
+        <v>709</v>
       </c>
       <c r="N516" t="s" s="2">
-        <v>464</v>
+        <v>179</v>
       </c>
       <c r="O516" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="P516" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>1358</v>
+      </c>
+      <c r="P516" s="2"/>
       <c r="Q516" t="s" s="2">
         <v>77</v>
       </c>
@@ -59827,7 +59835,7 @@
         <v>77</v>
       </c>
       <c r="AG516" t="s" s="2">
-        <v>467</v>
+        <v>1357</v>
       </c>
       <c r="AH516" t="s" s="2">
         <v>78</v>
@@ -59847,10 +59855,10 @@
         <v>1001</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1356</v>
+        <v>1359</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -59864,7 +59872,7 @@
         <v>86</v>
       </c>
       <c r="I517" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J517" t="s" s="2">
         <v>77</v>
@@ -59873,17 +59881,15 @@
         <v>77</v>
       </c>
       <c r="L517" t="s" s="2">
-        <v>708</v>
+        <v>87</v>
       </c>
       <c r="M517" t="s" s="2">
-        <v>709</v>
+        <v>88</v>
       </c>
       <c r="N517" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O517" t="s" s="2">
-        <v>1357</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O517" s="2"/>
       <c r="P517" s="2"/>
       <c r="Q517" t="s" s="2">
         <v>77</v>
@@ -59932,7 +59938,7 @@
         <v>77</v>
       </c>
       <c r="AG517" t="s" s="2">
-        <v>1356</v>
+        <v>90</v>
       </c>
       <c r="AH517" t="s" s="2">
         <v>78</v>
@@ -59944,7 +59950,7 @@
         <v>77</v>
       </c>
       <c r="AK517" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="518">
@@ -59952,21 +59958,21 @@
         <v>1001</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F518" s="2"/>
       <c r="G518" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H518" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I518" t="s" s="2">
         <v>77</v>
@@ -59978,15 +59984,17 @@
         <v>77</v>
       </c>
       <c r="L518" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M518" t="s" s="2">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="N518" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O518" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O518" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P518" s="2"/>
       <c r="Q518" t="s" s="2">
         <v>77</v>
@@ -60023,31 +60031,31 @@
         <v>77</v>
       </c>
       <c r="AC518" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD518" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE518" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF518" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG518" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AH518" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI518" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ518" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK518" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="519">
@@ -60055,42 +60063,42 @@
         <v>1001</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F519" s="2"/>
       <c r="G519" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H519" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I519" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J519" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K519" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L519" t="s" s="2">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M519" t="s" s="2">
-        <v>112</v>
+        <v>611</v>
       </c>
       <c r="N519" t="s" s="2">
-        <v>113</v>
+        <v>612</v>
       </c>
       <c r="O519" t="s" s="2">
-        <v>114</v>
+        <v>613</v>
       </c>
       <c r="P519" s="2"/>
       <c r="Q519" t="s" s="2">
@@ -60128,31 +60136,31 @@
         <v>77</v>
       </c>
       <c r="AC519" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD519" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE519" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF519" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>96</v>
+        <v>614</v>
       </c>
       <c r="AH519" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI519" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ519" t="s" s="2">
-        <v>77</v>
+        <v>615</v>
       </c>
       <c r="AK519" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="520">
@@ -60160,10 +60168,10 @@
         <v>1001</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -60177,7 +60185,7 @@
         <v>86</v>
       </c>
       <c r="I520" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J520" t="s" s="2">
         <v>77</v>
@@ -60186,16 +60194,16 @@
         <v>80</v>
       </c>
       <c r="L520" t="s" s="2">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="M520" t="s" s="2">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="N520" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="O520" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="P520" s="2"/>
       <c r="Q520" t="s" s="2">
@@ -60221,13 +60229,13 @@
         <v>77</v>
       </c>
       <c r="Y520" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="Z520" t="s" s="2">
-        <v>77</v>
+        <v>620</v>
       </c>
       <c r="AA520" t="s" s="2">
-        <v>77</v>
+        <v>621</v>
       </c>
       <c r="AB520" t="s" s="2">
         <v>77</v>
@@ -60245,7 +60253,7 @@
         <v>77</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="AH520" t="s" s="2">
         <v>78</v>
@@ -60254,7 +60262,7 @@
         <v>86</v>
       </c>
       <c r="AJ520" t="s" s="2">
-        <v>615</v>
+        <v>77</v>
       </c>
       <c r="AK520" t="s" s="2">
         <v>108</v>
@@ -60265,10 +60273,10 @@
         <v>1001</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -60282,7 +60290,7 @@
         <v>86</v>
       </c>
       <c r="I521" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J521" t="s" s="2">
         <v>77</v>
@@ -60291,16 +60299,16 @@
         <v>80</v>
       </c>
       <c r="L521" t="s" s="2">
-        <v>98</v>
+        <v>167</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="N521" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="O521" t="s" s="2">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="P521" s="2"/>
       <c r="Q521" t="s" s="2">
@@ -60326,13 +60334,13 @@
         <v>77</v>
       </c>
       <c r="Y521" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="Z521" t="s" s="2">
-        <v>620</v>
+        <v>77</v>
       </c>
       <c r="AA521" t="s" s="2">
-        <v>621</v>
+        <v>77</v>
       </c>
       <c r="AB521" t="s" s="2">
         <v>77</v>
@@ -60350,7 +60358,7 @@
         <v>77</v>
       </c>
       <c r="AG521" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="AH521" t="s" s="2">
         <v>78</v>
@@ -60370,10 +60378,10 @@
         <v>1001</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -60387,7 +60395,7 @@
         <v>86</v>
       </c>
       <c r="I522" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J522" t="s" s="2">
         <v>77</v>
@@ -60396,16 +60404,16 @@
         <v>80</v>
       </c>
       <c r="L522" t="s" s="2">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="M522" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="N522" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="O522" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="P522" s="2"/>
       <c r="Q522" t="s" s="2">
@@ -60455,7 +60463,7 @@
         <v>77</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="AH522" t="s" s="2">
         <v>78</v>
@@ -60475,10 +60483,10 @@
         <v>1001</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -60492,25 +60500,25 @@
         <v>86</v>
       </c>
       <c r="I523" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J523" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K523" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L523" t="s" s="2">
-        <v>87</v>
+        <v>1366</v>
       </c>
       <c r="M523" t="s" s="2">
-        <v>629</v>
+        <v>1367</v>
       </c>
       <c r="N523" t="s" s="2">
-        <v>630</v>
+        <v>1368</v>
       </c>
       <c r="O523" t="s" s="2">
-        <v>631</v>
+        <v>1369</v>
       </c>
       <c r="P523" s="2"/>
       <c r="Q523" t="s" s="2">
@@ -60560,7 +60568,7 @@
         <v>77</v>
       </c>
       <c r="AG523" t="s" s="2">
-        <v>632</v>
+        <v>1365</v>
       </c>
       <c r="AH523" t="s" s="2">
         <v>78</v>
@@ -60580,10 +60588,10 @@
         <v>1001</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1364</v>
+        <v>1370</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1364</v>
+        <v>1370</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -60597,7 +60605,7 @@
         <v>86</v>
       </c>
       <c r="I524" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J524" t="s" s="2">
         <v>77</v>
@@ -60606,17 +60614,15 @@
         <v>77</v>
       </c>
       <c r="L524" t="s" s="2">
-        <v>1365</v>
+        <v>87</v>
       </c>
       <c r="M524" t="s" s="2">
-        <v>1366</v>
+        <v>88</v>
       </c>
       <c r="N524" t="s" s="2">
-        <v>1367</v>
-      </c>
-      <c r="O524" t="s" s="2">
-        <v>1368</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O524" s="2"/>
       <c r="P524" s="2"/>
       <c r="Q524" t="s" s="2">
         <v>77</v>
@@ -60665,7 +60671,7 @@
         <v>77</v>
       </c>
       <c r="AG524" t="s" s="2">
-        <v>1364</v>
+        <v>90</v>
       </c>
       <c r="AH524" t="s" s="2">
         <v>78</v>
@@ -60677,7 +60683,7 @@
         <v>77</v>
       </c>
       <c r="AK524" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="525">
@@ -60685,21 +60691,21 @@
         <v>1001</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F525" s="2"/>
       <c r="G525" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H525" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I525" t="s" s="2">
         <v>77</v>
@@ -60711,15 +60717,17 @@
         <v>77</v>
       </c>
       <c r="L525" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M525" t="s" s="2">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="N525" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O525" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O525" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P525" s="2"/>
       <c r="Q525" t="s" s="2">
         <v>77</v>
@@ -60756,31 +60764,31 @@
         <v>77</v>
       </c>
       <c r="AC525" t="s" s="2">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="AD525" t="s" s="2">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="AE525" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF525" t="s" s="2">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="AG525" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AH525" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI525" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ525" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK525" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="526">
@@ -60788,42 +60796,42 @@
         <v>1001</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="F526" s="2"/>
       <c r="G526" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H526" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I526" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J526" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K526" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L526" t="s" s="2">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="M526" t="s" s="2">
-        <v>112</v>
+        <v>611</v>
       </c>
       <c r="N526" t="s" s="2">
-        <v>113</v>
+        <v>612</v>
       </c>
       <c r="O526" t="s" s="2">
-        <v>114</v>
+        <v>613</v>
       </c>
       <c r="P526" s="2"/>
       <c r="Q526" t="s" s="2">
@@ -60861,31 +60869,31 @@
         <v>77</v>
       </c>
       <c r="AC526" t="s" s="2">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="AD526" t="s" s="2">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="AE526" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AF526" t="s" s="2">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="AG526" t="s" s="2">
-        <v>96</v>
+        <v>614</v>
       </c>
       <c r="AH526" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI526" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ526" t="s" s="2">
-        <v>77</v>
+        <v>615</v>
       </c>
       <c r="AK526" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="527">
@@ -60893,10 +60901,10 @@
         <v>1001</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -60910,7 +60918,7 @@
         <v>86</v>
       </c>
       <c r="I527" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J527" t="s" s="2">
         <v>77</v>
@@ -60919,16 +60927,16 @@
         <v>80</v>
       </c>
       <c r="L527" t="s" s="2">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="M527" t="s" s="2">
-        <v>611</v>
+        <v>617</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>612</v>
+        <v>618</v>
       </c>
       <c r="O527" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="P527" s="2"/>
       <c r="Q527" t="s" s="2">
@@ -60954,13 +60962,13 @@
         <v>77</v>
       </c>
       <c r="Y527" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="Z527" t="s" s="2">
-        <v>77</v>
+        <v>620</v>
       </c>
       <c r="AA527" t="s" s="2">
-        <v>77</v>
+        <v>621</v>
       </c>
       <c r="AB527" t="s" s="2">
         <v>77</v>
@@ -60978,7 +60986,7 @@
         <v>77</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>78</v>
@@ -60987,7 +60995,7 @@
         <v>86</v>
       </c>
       <c r="AJ527" t="s" s="2">
-        <v>615</v>
+        <v>77</v>
       </c>
       <c r="AK527" t="s" s="2">
         <v>108</v>
@@ -60998,10 +61006,10 @@
         <v>1001</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -61015,7 +61023,7 @@
         <v>86</v>
       </c>
       <c r="I528" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J528" t="s" s="2">
         <v>77</v>
@@ -61024,16 +61032,16 @@
         <v>80</v>
       </c>
       <c r="L528" t="s" s="2">
-        <v>98</v>
+        <v>167</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>617</v>
+        <v>624</v>
       </c>
       <c r="N528" t="s" s="2">
-        <v>618</v>
+        <v>625</v>
       </c>
       <c r="O528" t="s" s="2">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="P528" s="2"/>
       <c r="Q528" t="s" s="2">
@@ -61059,13 +61067,13 @@
         <v>77</v>
       </c>
       <c r="Y528" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="Z528" t="s" s="2">
-        <v>620</v>
+        <v>77</v>
       </c>
       <c r="AA528" t="s" s="2">
-        <v>621</v>
+        <v>77</v>
       </c>
       <c r="AB528" t="s" s="2">
         <v>77</v>
@@ -61083,7 +61091,7 @@
         <v>77</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>622</v>
+        <v>627</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>78</v>
@@ -61103,10 +61111,10 @@
         <v>1001</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -61120,7 +61128,7 @@
         <v>86</v>
       </c>
       <c r="I529" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J529" t="s" s="2">
         <v>77</v>
@@ -61129,16 +61137,16 @@
         <v>80</v>
       </c>
       <c r="L529" t="s" s="2">
-        <v>167</v>
+        <v>87</v>
       </c>
       <c r="M529" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="N529" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="O529" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="P529" s="2"/>
       <c r="Q529" t="s" s="2">
@@ -61188,7 +61196,7 @@
         <v>77</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>78</v>
@@ -61208,10 +61216,10 @@
         <v>1001</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -61222,30 +61230,32 @@
         <v>78</v>
       </c>
       <c r="H530" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I530" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J530" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K530" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L530" t="s" s="2">
-        <v>87</v>
+        <v>178</v>
       </c>
       <c r="M530" t="s" s="2">
-        <v>629</v>
+        <v>1377</v>
       </c>
       <c r="N530" t="s" s="2">
-        <v>630</v>
+        <v>1378</v>
       </c>
       <c r="O530" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="P530" s="2"/>
+        <v>1379</v>
+      </c>
+      <c r="P530" t="s" s="2">
+        <v>1380</v>
+      </c>
       <c r="Q530" t="s" s="2">
         <v>77</v>
       </c>
@@ -61293,19 +61303,19 @@
         <v>77</v>
       </c>
       <c r="AG530" t="s" s="2">
-        <v>632</v>
+        <v>1376</v>
       </c>
       <c r="AH530" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI530" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ530" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK530" t="s" s="2">
-        <v>108</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="531">
@@ -61313,10 +61323,10 @@
         <v>1001</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1375</v>
+        <v>1382</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1375</v>
+        <v>1382</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -61327,10 +61337,10 @@
         <v>78</v>
       </c>
       <c r="H531" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I531" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J531" t="s" s="2">
         <v>77</v>
@@ -61339,20 +61349,16 @@
         <v>77</v>
       </c>
       <c r="L531" t="s" s="2">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="M531" t="s" s="2">
-        <v>1376</v>
+        <v>88</v>
       </c>
       <c r="N531" t="s" s="2">
-        <v>1377</v>
-      </c>
-      <c r="O531" t="s" s="2">
-        <v>1378</v>
-      </c>
-      <c r="P531" t="s" s="2">
-        <v>1379</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O531" s="2"/>
+      <c r="P531" s="2"/>
       <c r="Q531" t="s" s="2">
         <v>77</v>
       </c>
@@ -61400,19 +61406,19 @@
         <v>77</v>
       </c>
       <c r="AG531" t="s" s="2">
-        <v>1375</v>
+        <v>90</v>
       </c>
       <c r="AH531" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI531" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ531" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK531" t="s" s="2">
-        <v>1380</v>
+        <v>77</v>
       </c>
     </row>
     <row r="532">
@@ -61420,21 +61426,21 @@
         <v>1001</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F532" s="2"/>
       <c r="G532" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H532" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I532" t="s" s="2">
         <v>77</v>
@@ -61446,15 +61452,17 @@
         <v>77</v>
       </c>
       <c r="L532" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M532" t="s" s="2">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="N532" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O532" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O532" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P532" s="2"/>
       <c r="Q532" t="s" s="2">
         <v>77</v>
@@ -61503,19 +61511,19 @@
         <v>77</v>
       </c>
       <c r="AG532" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AH532" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI532" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ532" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK532" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="533">
@@ -61523,14 +61531,14 @@
         <v>1001</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="F533" s="2"/>
       <c r="G533" t="s" s="2">
@@ -61543,24 +61551,26 @@
         <v>77</v>
       </c>
       <c r="J533" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K533" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L533" t="s" s="2">
         <v>92</v>
       </c>
       <c r="M533" t="s" s="2">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="N533" t="s" s="2">
-        <v>113</v>
+        <v>185</v>
       </c>
       <c r="O533" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="P533" s="2"/>
+      <c r="P533" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="Q533" t="s" s="2">
         <v>77</v>
       </c>
@@ -61608,7 +61618,7 @@
         <v>77</v>
       </c>
       <c r="AG533" t="s" s="2">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="AH533" t="s" s="2">
         <v>78</v>
@@ -61628,46 +61638,42 @@
         <v>1001</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="F534" s="2"/>
       <c r="G534" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H534" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I534" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J534" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K534" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L534" t="s" s="2">
-        <v>92</v>
+        <v>1386</v>
       </c>
       <c r="M534" t="s" s="2">
-        <v>184</v>
+        <v>1387</v>
       </c>
       <c r="N534" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O534" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="P534" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>1388</v>
+      </c>
+      <c r="O534" s="2"/>
+      <c r="P534" s="2"/>
       <c r="Q534" t="s" s="2">
         <v>77</v>
       </c>
@@ -61715,19 +61721,19 @@
         <v>77</v>
       </c>
       <c r="AG534" t="s" s="2">
-        <v>187</v>
+        <v>1385</v>
       </c>
       <c r="AH534" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI534" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ534" t="s" s="2">
-        <v>77</v>
+        <v>1389</v>
       </c>
       <c r="AK534" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="535">
@@ -61735,10 +61741,10 @@
         <v>1001</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
@@ -61761,13 +61767,13 @@
         <v>77</v>
       </c>
       <c r="L535" t="s" s="2">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="M535" t="s" s="2">
-        <v>1386</v>
+        <v>1391</v>
       </c>
       <c r="N535" t="s" s="2">
-        <v>1387</v>
+        <v>1392</v>
       </c>
       <c r="O535" s="2"/>
       <c r="P535" s="2"/>
@@ -61818,7 +61824,7 @@
         <v>77</v>
       </c>
       <c r="AG535" t="s" s="2">
-        <v>1384</v>
+        <v>1390</v>
       </c>
       <c r="AH535" t="s" s="2">
         <v>78</v>
@@ -61827,7 +61833,7 @@
         <v>86</v>
       </c>
       <c r="AJ535" t="s" s="2">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="AK535" t="s" s="2">
         <v>108</v>
@@ -61838,10 +61844,10 @@
         <v>1001</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
@@ -61855,7 +61861,7 @@
         <v>86</v>
       </c>
       <c r="I536" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="J536" t="s" s="2">
         <v>77</v>
@@ -61864,16 +61870,20 @@
         <v>77</v>
       </c>
       <c r="L536" t="s" s="2">
-        <v>1385</v>
+        <v>422</v>
       </c>
       <c r="M536" t="s" s="2">
-        <v>1390</v>
+        <v>1394</v>
       </c>
       <c r="N536" t="s" s="2">
-        <v>1391</v>
-      </c>
-      <c r="O536" s="2"/>
-      <c r="P536" s="2"/>
+        <v>1395</v>
+      </c>
+      <c r="O536" t="s" s="2">
+        <v>1396</v>
+      </c>
+      <c r="P536" t="s" s="2">
+        <v>1397</v>
+      </c>
       <c r="Q536" t="s" s="2">
         <v>77</v>
       </c>
@@ -61897,13 +61907,13 @@
         <v>77</v>
       </c>
       <c r="Y536" t="s" s="2">
-        <v>77</v>
+        <v>373</v>
       </c>
       <c r="Z536" t="s" s="2">
-        <v>77</v>
+        <v>1398</v>
       </c>
       <c r="AA536" t="s" s="2">
-        <v>77</v>
+        <v>1399</v>
       </c>
       <c r="AB536" t="s" s="2">
         <v>77</v>
@@ -61921,7 +61931,7 @@
         <v>77</v>
       </c>
       <c r="AG536" t="s" s="2">
-        <v>1389</v>
+        <v>1393</v>
       </c>
       <c r="AH536" t="s" s="2">
         <v>78</v>
@@ -61930,7 +61940,7 @@
         <v>86</v>
       </c>
       <c r="AJ536" t="s" s="2">
-        <v>1388</v>
+        <v>77</v>
       </c>
       <c r="AK536" t="s" s="2">
         <v>108</v>
@@ -61941,10 +61951,10 @@
         <v>1001</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
@@ -61955,7 +61965,7 @@
         <v>78</v>
       </c>
       <c r="H537" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I537" t="s" s="2">
         <v>77</v>
@@ -61970,16 +61980,16 @@
         <v>422</v>
       </c>
       <c r="M537" t="s" s="2">
-        <v>1393</v>
+        <v>1401</v>
       </c>
       <c r="N537" t="s" s="2">
-        <v>1394</v>
+        <v>1402</v>
       </c>
       <c r="O537" t="s" s="2">
-        <v>1395</v>
+        <v>1403</v>
       </c>
       <c r="P537" t="s" s="2">
-        <v>1396</v>
+        <v>1404</v>
       </c>
       <c r="Q537" t="s" s="2">
         <v>77</v>
@@ -62004,13 +62014,13 @@
         <v>77</v>
       </c>
       <c r="Y537" t="s" s="2">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="Z537" t="s" s="2">
-        <v>1397</v>
+        <v>1405</v>
       </c>
       <c r="AA537" t="s" s="2">
-        <v>1398</v>
+        <v>1406</v>
       </c>
       <c r="AB537" t="s" s="2">
         <v>77</v>
@@ -62028,13 +62038,13 @@
         <v>77</v>
       </c>
       <c r="AG537" t="s" s="2">
-        <v>1392</v>
+        <v>1400</v>
       </c>
       <c r="AH537" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI537" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ537" t="s" s="2">
         <v>77</v>
@@ -62048,10 +62058,10 @@
         <v>1001</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1399</v>
+        <v>1407</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1399</v>
+        <v>1407</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
@@ -62062,7 +62072,7 @@
         <v>78</v>
       </c>
       <c r="H538" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I538" t="s" s="2">
         <v>77</v>
@@ -62074,19 +62084,17 @@
         <v>77</v>
       </c>
       <c r="L538" t="s" s="2">
-        <v>422</v>
+        <v>1310</v>
       </c>
       <c r="M538" t="s" s="2">
-        <v>1400</v>
+        <v>1408</v>
       </c>
       <c r="N538" t="s" s="2">
-        <v>1401</v>
-      </c>
-      <c r="O538" t="s" s="2">
-        <v>1402</v>
-      </c>
+        <v>1409</v>
+      </c>
+      <c r="O538" s="2"/>
       <c r="P538" t="s" s="2">
-        <v>1403</v>
+        <v>1410</v>
       </c>
       <c r="Q538" t="s" s="2">
         <v>77</v>
@@ -62111,13 +62119,13 @@
         <v>77</v>
       </c>
       <c r="Y538" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="Z538" t="s" s="2">
-        <v>1404</v>
+        <v>77</v>
       </c>
       <c r="AA538" t="s" s="2">
-        <v>1405</v>
+        <v>77</v>
       </c>
       <c r="AB538" t="s" s="2">
         <v>77</v>
@@ -62135,13 +62143,13 @@
         <v>77</v>
       </c>
       <c r="AG538" t="s" s="2">
-        <v>1399</v>
+        <v>1407</v>
       </c>
       <c r="AH538" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI538" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ538" t="s" s="2">
         <v>77</v>
@@ -62155,10 +62163,10 @@
         <v>1001</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1406</v>
+        <v>1411</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1406</v>
+        <v>1411</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -62181,18 +62189,16 @@
         <v>77</v>
       </c>
       <c r="L539" t="s" s="2">
-        <v>1309</v>
+        <v>87</v>
       </c>
       <c r="M539" t="s" s="2">
-        <v>1407</v>
+        <v>1412</v>
       </c>
       <c r="N539" t="s" s="2">
-        <v>1408</v>
+        <v>1413</v>
       </c>
       <c r="O539" s="2"/>
-      <c r="P539" t="s" s="2">
-        <v>1409</v>
-      </c>
+      <c r="P539" s="2"/>
       <c r="Q539" t="s" s="2">
         <v>77</v>
       </c>
@@ -62240,7 +62246,7 @@
         <v>77</v>
       </c>
       <c r="AG539" t="s" s="2">
-        <v>1406</v>
+        <v>1411</v>
       </c>
       <c r="AH539" t="s" s="2">
         <v>78</v>
@@ -62260,10 +62266,10 @@
         <v>1001</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
@@ -62274,7 +62280,7 @@
         <v>78</v>
       </c>
       <c r="H540" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I540" t="s" s="2">
         <v>77</v>
@@ -62283,18 +62289,20 @@
         <v>77</v>
       </c>
       <c r="K540" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L540" t="s" s="2">
-        <v>87</v>
+        <v>1415</v>
       </c>
       <c r="M540" t="s" s="2">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="N540" t="s" s="2">
-        <v>1412</v>
-      </c>
-      <c r="O540" s="2"/>
+        <v>1417</v>
+      </c>
+      <c r="O540" t="s" s="2">
+        <v>1418</v>
+      </c>
       <c r="P540" s="2"/>
       <c r="Q540" t="s" s="2">
         <v>77</v>
@@ -62343,13 +62351,13 @@
         <v>77</v>
       </c>
       <c r="AG540" t="s" s="2">
-        <v>1410</v>
+        <v>1414</v>
       </c>
       <c r="AH540" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI540" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ540" t="s" s="2">
         <v>77</v>
@@ -62363,10 +62371,10 @@
         <v>1001</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
@@ -62389,16 +62397,16 @@
         <v>80</v>
       </c>
       <c r="L541" t="s" s="2">
-        <v>1414</v>
+        <v>1420</v>
       </c>
       <c r="M541" t="s" s="2">
-        <v>1415</v>
+        <v>1421</v>
       </c>
       <c r="N541" t="s" s="2">
-        <v>1416</v>
+        <v>1422</v>
       </c>
       <c r="O541" t="s" s="2">
-        <v>1417</v>
+        <v>1423</v>
       </c>
       <c r="P541" s="2"/>
       <c r="Q541" t="s" s="2">
@@ -62448,7 +62456,7 @@
         <v>77</v>
       </c>
       <c r="AG541" t="s" s="2">
-        <v>1413</v>
+        <v>1419</v>
       </c>
       <c r="AH541" t="s" s="2">
         <v>78</v>
@@ -62468,10 +62476,10 @@
         <v>1001</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
@@ -62494,18 +62502,20 @@
         <v>80</v>
       </c>
       <c r="L542" t="s" s="2">
-        <v>1419</v>
+        <v>178</v>
       </c>
       <c r="M542" t="s" s="2">
-        <v>1420</v>
+        <v>1425</v>
       </c>
       <c r="N542" t="s" s="2">
-        <v>1421</v>
+        <v>1426</v>
       </c>
       <c r="O542" t="s" s="2">
-        <v>1422</v>
-      </c>
-      <c r="P542" s="2"/>
+        <v>1427</v>
+      </c>
+      <c r="P542" t="s" s="2">
+        <v>1428</v>
+      </c>
       <c r="Q542" t="s" s="2">
         <v>77</v>
       </c>
@@ -62553,7 +62563,7 @@
         <v>77</v>
       </c>
       <c r="AG542" t="s" s="2">
-        <v>1418</v>
+        <v>1424</v>
       </c>
       <c r="AH542" t="s" s="2">
         <v>78</v>
@@ -62573,10 +62583,10 @@
         <v>1001</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1423</v>
+        <v>1429</v>
       </c>
       <c r="D543" s="2"/>
       <c r="E543" t="s" s="2">
@@ -62587,7 +62597,7 @@
         <v>78</v>
       </c>
       <c r="H543" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I543" t="s" s="2">
         <v>77</v>
@@ -62596,23 +62606,19 @@
         <v>77</v>
       </c>
       <c r="K543" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L543" t="s" s="2">
-        <v>178</v>
+        <v>87</v>
       </c>
       <c r="M543" t="s" s="2">
-        <v>1424</v>
+        <v>88</v>
       </c>
       <c r="N543" t="s" s="2">
-        <v>1425</v>
-      </c>
-      <c r="O543" t="s" s="2">
-        <v>1426</v>
-      </c>
-      <c r="P543" t="s" s="2">
-        <v>1427</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="O543" s="2"/>
+      <c r="P543" s="2"/>
       <c r="Q543" t="s" s="2">
         <v>77</v>
       </c>
@@ -62660,19 +62666,19 @@
         <v>77</v>
       </c>
       <c r="AG543" t="s" s="2">
-        <v>1423</v>
+        <v>90</v>
       </c>
       <c r="AH543" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI543" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ543" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK543" t="s" s="2">
-        <v>108</v>
+        <v>77</v>
       </c>
     </row>
     <row r="544">
@@ -62680,21 +62686,21 @@
         <v>1001</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="D544" s="2"/>
       <c r="E544" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="F544" s="2"/>
       <c r="G544" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H544" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I544" t="s" s="2">
         <v>77</v>
@@ -62706,15 +62712,17 @@
         <v>77</v>
       </c>
       <c r="L544" t="s" s="2">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="M544" t="s" s="2">
-        <v>88</v>
+        <v>112</v>
       </c>
       <c r="N544" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="O544" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="O544" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="P544" s="2"/>
       <c r="Q544" t="s" s="2">
         <v>77</v>
@@ -62763,19 +62771,19 @@
         <v>77</v>
       </c>
       <c r="AG544" t="s" s="2">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="AH544" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI544" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ544" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK544" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="545">
@@ -62783,14 +62791,14 @@
         <v>1001</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="F545" s="2"/>
       <c r="G545" t="s" s="2">
@@ -62803,24 +62811,26 @@
         <v>77</v>
       </c>
       <c r="J545" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K545" t="s" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="L545" t="s" s="2">
         <v>92</v>
       </c>
       <c r="M545" t="s" s="2">
-        <v>112</v>
+        <v>184</v>
       </c>
       <c r="N545" t="s" s="2">
-        <v>113</v>
+        <v>185</v>
       </c>
       <c r="O545" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="P545" s="2"/>
+      <c r="P545" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="Q545" t="s" s="2">
         <v>77</v>
       </c>
@@ -62868,7 +62878,7 @@
         <v>77</v>
       </c>
       <c r="AG545" t="s" s="2">
-        <v>96</v>
+        <v>187</v>
       </c>
       <c r="AH545" t="s" s="2">
         <v>78</v>
@@ -62888,45 +62898,45 @@
         <v>1001</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="F546" s="2"/>
       <c r="G546" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H546" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="I546" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J546" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K546" t="s" s="2">
         <v>80</v>
       </c>
       <c r="L546" t="s" s="2">
-        <v>92</v>
+        <v>422</v>
       </c>
       <c r="M546" t="s" s="2">
-        <v>184</v>
+        <v>1433</v>
       </c>
       <c r="N546" t="s" s="2">
-        <v>185</v>
+        <v>1434</v>
       </c>
       <c r="O546" t="s" s="2">
-        <v>114</v>
+        <v>1435</v>
       </c>
       <c r="P546" t="s" s="2">
-        <v>186</v>
+        <v>1142</v>
       </c>
       <c r="Q546" t="s" s="2">
         <v>77</v>
@@ -62951,13 +62961,13 @@
         <v>77</v>
       </c>
       <c r="Y546" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="Z546" t="s" s="2">
-        <v>77</v>
+        <v>1143</v>
       </c>
       <c r="AA546" t="s" s="2">
-        <v>77</v>
+        <v>1144</v>
       </c>
       <c r="AB546" t="s" s="2">
         <v>77</v>
@@ -62975,19 +62985,19 @@
         <v>77</v>
       </c>
       <c r="AG546" t="s" s="2">
-        <v>187</v>
+        <v>1432</v>
       </c>
       <c r="AH546" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AI546" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AJ546" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AK546" t="s" s="2">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="547">
@@ -62995,10 +63005,10 @@
         <v>1001</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1431</v>
+        <v>1436</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1431</v>
+        <v>1436</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -63006,7 +63016,7 @@
       </c>
       <c r="F547" s="2"/>
       <c r="G547" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="H547" t="s" s="2">
         <v>86</v>
@@ -63021,19 +63031,19 @@
         <v>80</v>
       </c>
       <c r="L547" t="s" s="2">
-        <v>422</v>
+        <v>1437</v>
       </c>
       <c r="M547" t="s" s="2">
-        <v>1432</v>
+        <v>1438</v>
       </c>
       <c r="N547" t="s" s="2">
-        <v>1433</v>
+        <v>1222</v>
       </c>
       <c r="O547" t="s" s="2">
-        <v>1434</v>
+        <v>1439</v>
       </c>
       <c r="P547" t="s" s="2">
-        <v>1141</v>
+        <v>1215</v>
       </c>
       <c r="Q547" t="s" s="2">
         <v>77</v>
@@ -63058,34 +63068,34 @@
         <v>77</v>
       </c>
       <c r="Y547" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="Z547" t="s" s="2">
-        <v>1435</v>
+        <v>77</v>
       </c>
       <c r="AA547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF547" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AG547" t="s" s="2">
         <v>1436</v>
       </c>
-      <c r="AB547" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC547" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD547" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE547" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF547" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG547" t="s" s="2">
-        <v>1431</v>
-      </c>
       <c r="AH547" t="s" s="2">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="AI547" t="s" s="2">
         <v>86</v>
@@ -63102,10 +63112,10 @@
         <v>1001</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -63125,22 +63135,22 @@
         <v>77</v>
       </c>
       <c r="K548" t="s" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="L548" t="s" s="2">
-        <v>1438</v>
+        <v>422</v>
       </c>
       <c r="M548" t="s" s="2">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="N548" t="s" s="2">
-        <v>1209</v>
+        <v>1442</v>
       </c>
       <c r="O548" t="s" s="2">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="P548" t="s" s="2">
-        <v>1202</v>
+        <v>1318</v>
       </c>
       <c r="Q548" t="s" s="2">
         <v>77</v>
@@ -63165,13 +63175,13 @@
         <v>77</v>
       </c>
       <c r="Y548" t="s" s="2">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="Z548" t="s" s="2">
-        <v>77</v>
+        <v>1319</v>
       </c>
       <c r="AA548" t="s" s="2">
-        <v>77</v>
+        <v>1320</v>
       </c>
       <c r="AB548" t="s" s="2">
         <v>77</v>
@@ -63189,7 +63199,7 @@
         <v>77</v>
       </c>
       <c r="AG548" t="s" s="2">
-        <v>1437</v>
+        <v>1440</v>
       </c>
       <c r="AH548" t="s" s="2">
         <v>78</v>
@@ -63198,7 +63208,7 @@
         <v>86</v>
       </c>
       <c r="AJ548" t="s" s="2">
-        <v>77</v>
+        <v>1321</v>
       </c>
       <c r="AK548" t="s" s="2">
         <v>108</v>
@@ -63209,21 +63219,21 @@
         <v>1001</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
-        <v>77</v>
+        <v>1323</v>
       </c>
       <c r="F549" s="2"/>
       <c r="G549" t="s" s="2">
         <v>78</v>
       </c>
       <c r="H549" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="I549" t="s" s="2">
         <v>77</v>
@@ -63238,16 +63248,16 @@
         <v>422</v>
       </c>
       <c r="M549" t="s" s="2">
-        <v>1442</v>
+        <v>1445</v>
       </c>
       <c r="N549" t="s" s="2">
-        <v>1443</v>
+        <v>1446</v>
       </c>
       <c r="O549" t="s" s="2">
-        <v>1444</v>
+        <v>1326</v>
       </c>
       <c r="P549" t="s" s="2">
-        <v>1317</v>
+        <v>1327</v>
       </c>
       <c r="Q549" t="s" s="2">
         <v>77</v>
@@ -63275,10 +63285,10 @@
         <v>106</v>
       </c>
       <c r="Z549" t="s" s="2">
-        <v>1318</v>
+        <v>1328</v>
       </c>
       <c r="AA549" t="s" s="2">
-        <v>1319</v>
+        <v>1329</v>
       </c>
       <c r="AB549" t="s" s="2">
         <v>77</v>
@@ -63296,16 +63306,16 @@
         <v>77</v>
       </c>
       <c r="AG549" t="s" s="2">
-        <v>1441</v>
+        <v>1444</v>
       </c>
       <c r="AH549" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AI549" t="s" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="AJ549" t="s" s="2">
-        <v>1320</v>
+        <v>77</v>
       </c>
       <c r="AK549" t="s" s="2">
         <v>108</v>
@@ -63316,14 +63326,14 @@
         <v>1001</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
-        <v>1322</v>
+        <v>77</v>
       </c>
       <c r="F550" s="2"/>
       <c r="G550" t="s" s="2">
@@ -63342,19 +63352,19 @@
         <v>77</v>
       </c>
       <c r="L550" t="s" s="2">
-        <v>422</v>
+        <v>81</v>
       </c>
       <c r="M550" t="s" s="2">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="N550" t="s" s="2">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="O550" t="s" s="2">
-        <v>1325</v>
+        <v>1379</v>
       </c>
       <c r="P550" t="s" s="2">
-        <v>1326</v>
+        <v>1380</v>
       </c>
       <c r="Q550" t="s" s="2">
         <v>77</v>
@@ -63379,13 +63389,13 @@
         <v>77</v>
       </c>
       <c r="Y550" t="s" s="2">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="Z550" t="s" s="2">
-        <v>1327</v>
+        <v>77</v>
       </c>
       <c r="AA550" t="s" s="2">
-        <v>1328</v>
+        <v>77</v>
       </c>
       <c r="AB550" t="s" s="2">
         <v>77</v>
@@ -63403,7 +63413,7 @@
         <v>77</v>
       </c>
       <c r="AG550" t="s" s="2">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="AH550" t="s" s="2">
         <v>78</v>
@@ -63415,113 +63425,6 @@
         <v>77</v>
       </c>
       <c r="AK550" t="s" s="2">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="551">
-      <c r="A551" t="s" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B551" t="s" s="2">
-        <v>1448</v>
-      </c>
-      <c r="C551" t="s" s="2">
-        <v>1448</v>
-      </c>
-      <c r="D551" s="2"/>
-      <c r="E551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="F551" s="2"/>
-      <c r="G551" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H551" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="L551" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="M551" t="s" s="2">
-        <v>1449</v>
-      </c>
-      <c r="N551" t="s" s="2">
-        <v>1450</v>
-      </c>
-      <c r="O551" t="s" s="2">
-        <v>1378</v>
-      </c>
-      <c r="P551" t="s" s="2">
-        <v>1379</v>
-      </c>
-      <c r="Q551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="R551" s="2"/>
-      <c r="S551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AG551" t="s" s="2">
-        <v>1448</v>
-      </c>
-      <c r="AH551" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AI551" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ551" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK551" t="s" s="2">
         <v>108</v>
       </c>
     </row>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-24T13:49:26+00:00</t>
+    <t>2026-08-28T09:59:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:59:02+00:00</t>
+    <t>2026-08-28T10:19:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T10:19:24+00:00</t>
+    <t>2026-09-01T07:28:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18409" uniqueCount="1450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18409" uniqueCount="1452">
   <si>
     <t>Property</t>
   </si>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T07:28:55+00:00</t>
+    <t>2026-09-01T08:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4154,10 +4154,10 @@
     <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
   </si>
   <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+    <t>Eingeschränkte Auswahl aus HL7 v3 ObservationInterpretation. FHIR bindet dieses Element extensible an das vollständige ValueSet Observation Interpretation Codes; das Modul schränkt auf die im Laborkontext sinnvollen Konzepte ein. Lokale Kodierungen wie -- - N + ++ oder L N H lassen sich darauf abbilden. Da die Bindung extensible ist, dürfen darüber hinaus weitere Codes verwendet werden; praktisch relevant sind die abnormal-Codes HH, LL und AA, etwa für Werte jenseits der Telefongrenze.</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/core/modul-labor/ValueSet/Interpretation</t>
   </si>
   <si>
     <t>Observation.note</t>
@@ -4518,6 +4518,12 @@
   </si>
   <si>
     <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
+  </si>
+  <si>
+    <t>Codes identifying interpretations of observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -5716,7 +5722,7 @@
     <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="140.3671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="255.0" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="100.98046875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -63285,10 +63291,10 @@
         <v>106</v>
       </c>
       <c r="Z549" t="s" s="2">
-        <v>1328</v>
+        <v>1447</v>
       </c>
       <c r="AA549" t="s" s="2">
-        <v>1329</v>
+        <v>1448</v>
       </c>
       <c r="AB549" t="s" s="2">
         <v>77</v>
@@ -63326,10 +63332,10 @@
         <v>1001</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -63355,10 +63361,10 @@
         <v>81</v>
       </c>
       <c r="M550" t="s" s="2">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="N550" t="s" s="2">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="O550" t="s" s="2">
         <v>1379</v>
@@ -63413,7 +63419,7 @@
         <v>77</v>
       </c>
       <c r="AG550" t="s" s="2">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="AH550" t="s" s="2">
         <v>78</v>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T08:17:52+00:00</t>
+    <t>2026-09-01T11:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:26:20+00:00</t>
+    <t>2026-09-01T11:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:37:07+00:00</t>
+    <t>2026-09-01T11:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:44:40+00:00</t>
+    <t>2026-09-01T12:05:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:05:15+00:00</t>
+    <t>2026-09-01T12:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:12:27+00:00</t>
+    <t>2026-09-01T12:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:31:59+00:00</t>
+    <t>2026-09-01T12:37:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:37:11+00:00</t>
+    <t>2026-09-01T12:41:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:41:57+00:00</t>
+    <t>2026-09-01T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:58:26+00:00</t>
+    <t>2026-09-01T13:38:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:38:20+00:00</t>
+    <t>2026-09-01T13:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:44:38+00:00</t>
+    <t>2026-09-01T14:35:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T14:35:41+00:00</t>
+    <t>2026-09-01T15:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3847,7 +3847,7 @@
     <t>pqTranslation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {extension-quantity-translation}
+    <t xml:space="preserve">Extension {extension-quantity-translation|5.2.0}
 </t>
   </si>
   <si>
@@ -3904,7 +3904,7 @@
     <t>quantityPrecision</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {quantity-precision}
+    <t xml:space="preserve">Extension {quantity-precision|5.2.0}
 </t>
   </si>
   <si>
@@ -56042,7 +56042,7 @@
         <v>79</v>
       </c>
       <c r="AJ480" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK480" t="s" s="2">
         <v>84</v>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:11:46+00:00</t>
+    <t>2026-09-01T15:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:27:37+00:00</t>
+    <t>2026-09-01T15:32:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:32:49+00:00</t>
+    <t>2026-09-01T15:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T15:38:53+00:00</t>
+    <t>2026-09-01T16:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:17:13+00:00</t>
+    <t>2026-09-01T16:23:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T16:23:29+00:00</t>
+    <t>2026-09-02T06:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:57:39+00:00</t>
+    <t>2026-09-02T07:24:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T07:24:40+00:00</t>
+    <t>2026-09-02T08:07:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T08:07:59+00:00</t>
+    <t>2026-09-02T09:10:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:10:52+00:00</t>
+    <t>2026-09-02T09:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:21:54+00:00</t>
+    <t>2026-09-02T10:32:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:32:32+00:00</t>
+    <t>2026-09-02T10:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T10:47:13+00:00</t>
+    <t>2026-09-02T11:41:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ig-publisher-migration/all-profiles.xlsx
+++ b/branches/ig-publisher-migration/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T11:41:16+00:00</t>
+    <t>2026-09-02T11:51:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
